--- a/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
+++ b/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hinam\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433EF4CD-7EB4-4C9B-A134-2A92F47F3384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="フォームの回答 1" sheetId="1" r:id="rId5"/>
+    <sheet name="フォームの回答 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>タイムスタンプ</t>
   </si>
@@ -127,99 +136,63 @@
     <t>お客様向け参加証(缶バッチ)　販売希望数は？</t>
   </si>
   <si>
-    <t>テスト</t>
-  </si>
-  <si>
     <t>参加する</t>
   </si>
   <si>
+    <t>三軒家東</t>
+  </si>
+  <si>
+    <t>焼肉・ホルモン</t>
+  </si>
+  <si>
+    <t>テールブあり</t>
+  </si>
+  <si>
+    <t>腹ごしらえ</t>
+  </si>
+  <si>
+    <t>テイクアウトOK</t>
+  </si>
+  <si>
+    <t>全て</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード</t>
+  </si>
+  <si>
+    <t>はい。希望します。</t>
+  </si>
+  <si>
+    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
+  </si>
+  <si>
+    <t>メラゾーマセット</t>
+  </si>
+  <si>
+    <t>1ドリンク+紅白盛り(赤身、ホルモン)</t>
+  </si>
+  <si>
+    <t>お好きなドリンク(アルコール、ノンアル)と名物の焼肉盛り合わせがセット</t>
+  </si>
+  <si>
+    <t>2,000円</t>
+  </si>
+  <si>
+    <t>無し</t>
+  </si>
+  <si>
+    <t>？？？？？</t>
+  </si>
+  <si>
+    <t>500円</t>
+  </si>
+  <si>
+    <t>Tようび</t>
+  </si>
+  <si>
     <t>三軒家西</t>
   </si>
   <si>
-    <t>クレープ</t>
-  </si>
-  <si>
-    <t>テールブあり</t>
-  </si>
-  <si>
-    <t>ひと休み</t>
-  </si>
-  <si>
-    <t>テイクアウトOK</t>
-  </si>
-  <si>
-    <t>火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
-  </si>
-  <si>
-    <t>現金</t>
-  </si>
-  <si>
-    <t>はい。希望します。</t>
-  </si>
-  <si>
-    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
-  </si>
-  <si>
-    <t>クレープとコーヒーセット</t>
-  </si>
-  <si>
-    <t>チョコバナナとハンドドリップコーヒーのセットです</t>
-  </si>
-  <si>
-    <t>マリオカートタイムアタックチャレンジ</t>
-  </si>
-  <si>
-    <t>マリオサーキットを2分でクリアできらスタンプ1個</t>
-  </si>
-  <si>
-    <t>100円</t>
-  </si>
-  <si>
-    <t>1人1日1回です</t>
-  </si>
-  <si>
-    <t>大正焼肉SUNナスビ！！</t>
-  </si>
-  <si>
-    <t>三軒家東</t>
-  </si>
-  <si>
-    <t>焼肉・ホルモン</t>
-  </si>
-  <si>
-    <t>腹ごしらえ</t>
-  </si>
-  <si>
-    <t>全て</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード</t>
-  </si>
-  <si>
-    <t>メラゾーマセット</t>
-  </si>
-  <si>
-    <t>1ドリンク+紅白盛り(赤身、ホルモン)</t>
-  </si>
-  <si>
-    <t>お好きなドリンク(アルコール、ノンアル)と名物の焼肉盛り合わせがセット</t>
-  </si>
-  <si>
-    <t>2,000円</t>
-  </si>
-  <si>
-    <t>無し</t>
-  </si>
-  <si>
-    <t>？？？？？</t>
-  </si>
-  <si>
-    <t>500円</t>
-  </si>
-  <si>
-    <t>Tようび</t>
-  </si>
-  <si>
     <t>おばんざい</t>
   </si>
   <si>
@@ -256,9 +229,6 @@
     <t>おばんざいが無くなるまで。</t>
   </si>
   <si>
-    <t>ハンバーガー・ママ</t>
-  </si>
-  <si>
     <t>ハンバーガー</t>
   </si>
   <si>
@@ -283,27 +253,103 @@
     <t>お酒もソフトもほとんどのドリンクがお選び頂けます</t>
   </si>
   <si>
-    <t>参加しない</t>
+    <t>バーガー酒場ハンバーガー・ママ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>大正焼肉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SUN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ナスビ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!!</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -311,91 +357,46 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="19" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="19" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="19" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -412,74 +413,98 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="フォームの回答 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="フォームの回答 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AL6" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:AL4">
   <tableColumns count="38">
-    <tableColumn name="タイムスタンプ" id="1"/>
-    <tableColumn name="店名" id="2"/>
-    <tableColumn name="大正酔いどれクエストⅡに参加されますか？" id="3"/>
-    <tableColumn name="  エリア  " id="4"/>
-    <tableColumn name="カテゴリ" id="5"/>
-    <tableColumn name="スタイル" id="6"/>
-    <tableColumn name="タイプ" id="7"/>
-    <tableColumn name="テイクアウト" id="8"/>
-    <tableColumn name="提供曜日" id="9"/>
-    <tableColumn name="提供時間：開始" id="10"/>
-    <tableColumn name="提供時間：終了" id="11"/>
-    <tableColumn name="提供時間に対する補足" id="12"/>
-    <tableColumn name="決済方法" id="13"/>
-    <tableColumn name="店舗クーポンを希望されますか？" id="14"/>
-    <tableColumn name="  「どれクエⅡ」にはどの企画で参加されますか？  " id="15"/>
-    <tableColumn name="  酔いどれセット名  " id="16"/>
-    <tableColumn name="  酔いどれセット内容  " id="17"/>
-    <tableColumn name="セット内容備考" id="18"/>
-    <tableColumn name="  価格(税込)  " id="19"/>
-    <tableColumn name="チャージ料(税込)" id="20"/>
-    <tableColumn name="限定数量" id="21"/>
-    <tableColumn name="クエスト名" id="22"/>
-    <tableColumn name="クエスト内容/報酬" id="23"/>
-    <tableColumn name="クエスト料金(税込)" id="24"/>
-    <tableColumn name="クエストチャージ料 (税込)" id="25"/>
-    <tableColumn name="クエスト備考" id="26"/>
-    <tableColumn name="酔いどれセット名" id="27"/>
-    <tableColumn name="  酔いどれセット内容   2" id="28"/>
-    <tableColumn name="セット内容備考 2" id="29"/>
-    <tableColumn name="価格(税込)" id="30"/>
-    <tableColumn name="チャージ料(税込) 2" id="31"/>
-    <tableColumn name="限定数量 2" id="32"/>
-    <tableColumn name="クエスト名 2" id="33"/>
-    <tableColumn name="クエスト内容/報酬 2" id="34"/>
-    <tableColumn name="クエスト料金(税込) 2" id="35"/>
-    <tableColumn name="クエストチャージ料 (税込) 2" id="36"/>
-    <tableColumn name="クエスト備考 2" id="37"/>
-    <tableColumn name="お客様向け参加証(缶バッチ)　販売希望数は？" id="38"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="タイムスタンプ"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="店名"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="大正酔いどれクエストⅡに参加されますか？"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="  エリア  "/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="カテゴリ"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="スタイル"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="タイプ"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="テイクアウト"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="提供曜日"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="提供時間：開始"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="提供時間：終了"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="提供時間に対する補足"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="決済方法"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="店舗クーポンを希望されますか？"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="  「どれクエⅡ」にはどの企画で参加されますか？  "/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="  酔いどれセット名  "/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="  酔いどれセット内容  "/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="セット内容備考"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="  価格(税込)  "/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="チャージ料(税込)"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="限定数量"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="クエスト名"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="クエスト内容/報酬"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="クエスト料金(税込)"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="クエストチャージ料 (税込)"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="クエスト備考"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="酔いどれセット名"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="  酔いどれセット内容   2"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="セット内容備考 2"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="価格(税込)"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="チャージ料(税込) 2"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="限定数量 2"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="クエスト名 2"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="クエスト内容/報酬 2"/>
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="クエスト料金(税込) 2"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="クエストチャージ料 (税込) 2"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="クエスト備考 2"/>
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="お客様向け参加証(缶バッチ)　販売希望数は？"/>
   </tableColumns>
-  <tableStyleInfo name="フォームの回答 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="フォームの回答 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -669,24 +694,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AL4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="20.0"/>
-    <col customWidth="1" min="4" max="14" width="18.88"/>
-    <col customWidth="1" min="15" max="15" width="43.75"/>
-    <col customWidth="1" min="16" max="44" width="18.88"/>
+    <col min="1" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="14" width="18.85546875" customWidth="1"/>
+    <col min="15" max="15" width="43.7109375" customWidth="1"/>
+    <col min="16" max="44" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:38" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,308 +826,210 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="3">
-        <v>46280.342201064814</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:38" ht="22.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>46280.616818807874</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="5">
-        <v>0.7916666666642413</v>
-      </c>
-      <c r="K2" s="5">
-        <v>0.9375</v>
-      </c>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="AA2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="4" t="s">
+      <c r="AB2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AC2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="4">
-        <v>1000.0</v>
-      </c>
-      <c r="AE2" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="AF2" s="4">
-        <v>20.0</v>
-      </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AD2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AH2" s="4" t="s">
+      <c r="AE2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="AG2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AJ2" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="AK2" s="4" t="s">
+      <c r="AH2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AL2" s="7"/>
+      <c r="AJ2" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="8">
-        <v>46280.616818807874</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:38" ht="22.5" customHeight="1">
+      <c r="A3" s="2">
+        <v>46280.631479247684</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.70833333333575865</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.91666666666424135</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="22.5" customHeight="1">
+      <c r="A4" s="2">
+        <v>46280.814136759262</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="E4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0.625</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0.9375</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA3" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="9" t="s">
+      <c r="H4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AC3" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD3" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE3" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ3" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="8">
-        <v>46280.631479247684</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="10">
-        <v>0.7083333333357587</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0.9166666666642413</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="O4" s="9" t="s">
+      <c r="P4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="Q4" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="R4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="R4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="8">
-        <v>46280.81413675926</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="S5" s="9">
-        <v>1000.0</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="8">
-        <v>46282.69798508102</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>90</v>
+      <c r="S4" s="3">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
+++ b/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="シート1" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'フォームの回答 1'!$A$1:$AQ$21</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'フォームの回答 1'!$A$1:$AQ$26</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="494">
   <si>
     <t>ID</t>
   </si>
@@ -88,25 +88,55 @@
     <t>https://www.instagram.com/sunnasubi0675085821</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目５−１０</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</t>
+  </si>
+  <si>
+    <t>大正居酒屋タイガーパンチ</t>
+  </si>
+  <si>
+    <t>創作ガチ中華</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/taipan_taisho</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目５−１３</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</t>
+  </si>
+  <si>
+    <t>ハイエナハイツ</t>
+  </si>
+  <si>
+    <t>ジビエ・肉料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haiena_haitu</t>
+  </si>
+  <si>
     <t>タイムスタンプ</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目５−１０</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</t>
+    <t>大阪市大正区三軒家西１丁目５−７</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
   </si>
   <si>
     <t>店名</t>
   </si>
   <si>
-    <t>大正居酒屋タイガーパンチ</t>
-  </si>
-  <si>
-    <t>創作ガチ中華</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/taipan_taisho</t>
+    <t>CHWEETS</t>
+  </si>
+  <si>
+    <t>クレープ酒場・夜カフェ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chweets_1138</t>
   </si>
   <si>
     <t>大正酔いどれクエストⅡに参加されますか？</t>
@@ -121,13 +151,13 @@
     <t>スタイル</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家西１丁目１７−１７</t>
+  </si>
+  <si>
     <t>タイプ</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目５−１３</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</t>
+    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
   </si>
   <si>
     <t>テイクアウト</t>
@@ -142,21 +172,21 @@
     <t>どれクエ対応時間：終了</t>
   </si>
   <si>
+    <t>BAR K'S〜ケーズ〜</t>
+  </si>
+  <si>
+    <t>ダーツ・カラオケ</t>
+  </si>
+  <si>
     <t>提供時間に対する補足</t>
   </si>
   <si>
+    <t>https://www.instagram.com/bar_ks_taisho</t>
+  </si>
+  <si>
     <t>決済方法</t>
   </si>
   <si>
-    <t>ハイエナハイツ</t>
-  </si>
-  <si>
-    <t>ジビエ・肉料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/haiena_haitu</t>
-  </si>
-  <si>
     <t>店舗クーポンを希望されますか？</t>
   </si>
   <si>
@@ -169,18 +199,18 @@
     <t xml:space="preserve">  酔いどれセット内容  </t>
   </si>
   <si>
+    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2D</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
+  </si>
+  <si>
     <t>セット内容備考</t>
   </si>
   <si>
     <t xml:space="preserve">  価格(税込)  </t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目５−７</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
-  </si>
-  <si>
     <t>チャージ料(税込)</t>
   </si>
   <si>
@@ -190,30 +220,36 @@
     <t>クエスト名</t>
   </si>
   <si>
+    <t>Bar Six Nine</t>
+  </si>
+  <si>
+    <t>ショットバー</t>
+  </si>
+  <si>
     <t>クエスト内容/報酬</t>
   </si>
   <si>
+    <t>https://www.instagram.com/bar_six_nine_0692</t>
+  </si>
+  <si>
     <t>クエスト料金(税込)</t>
   </si>
   <si>
     <t>クエストチャージ料 (税込)</t>
   </si>
   <si>
-    <t>CHWEETS</t>
-  </si>
-  <si>
-    <t>クレープ酒場・夜カフェ</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chweets_1138</t>
-  </si>
-  <si>
     <t>クエスト備考</t>
   </si>
   <si>
     <t>酔いどれセット名</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目５</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
+  </si>
+  <si>
     <t xml:space="preserve">  酔いどれセット内容   2</t>
   </si>
   <si>
@@ -226,15 +262,18 @@
     <t>チャージ料(税込) 2</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目１７−１７</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
+    <t>B.B.QホルモンMOU</t>
   </si>
   <si>
     <t>限定数量 2</t>
   </si>
   <si>
+    <t>立ち飲み・ホルモン</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bbq.mou.29</t>
+  </si>
+  <si>
     <t>クエスト名 2</t>
   </si>
   <si>
@@ -247,91 +286,13 @@
     <t>クエストチャージ料 (税込) 2</t>
   </si>
   <si>
-    <t>BAR K'S〜ケーズ〜</t>
-  </si>
-  <si>
     <t>クエスト備考 2</t>
   </si>
   <si>
-    <t>ダーツ・カラオケ</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_ks_taisho</t>
+    <t>大阪市大正区三軒家東１丁目２−４</t>
   </si>
   <si>
     <t>お客様向け参加証(缶バッチ)　販売希望数は？</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2D</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
-  </si>
-  <si>
-    <t>Bar Six Nine</t>
-  </si>
-  <si>
-    <t>ショットバー</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_six_nine_0692</t>
-  </si>
-  <si>
-    <t>参加する</t>
-  </si>
-  <si>
-    <t>三軒家西</t>
-  </si>
-  <si>
-    <t>おばんざい</t>
-  </si>
-  <si>
-    <t>テールブあり</t>
-  </si>
-  <si>
-    <t>サク飲み</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
-  </si>
-  <si>
-    <t>テイクアウトOK</t>
-  </si>
-  <si>
-    <t>日曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
-  </si>
-  <si>
-    <t>土日祝は15時～22時</t>
-  </si>
-  <si>
-    <t>B.B.QホルモンMOU</t>
-  </si>
-  <si>
-    <t>立ち飲み・ホルモン</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bbq.mou.29</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード, d払い、楽天pay、aupay、wesmo</t>
-  </si>
-  <si>
-    <t>はい。希望します。</t>
-  </si>
-  <si>
-    <t>「酔いどれセット」のみで参加</t>
-  </si>
-  <si>
-    <t>選べるおばんざい3種セット</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目２−４</t>
-  </si>
-  <si>
-    <t>おばんざい小盛3種+ドリンク1杯</t>
   </si>
   <si>
     <r>
@@ -345,63 +306,102 @@
     </r>
   </si>
   <si>
+    <t>だしと鶏ちゃぼ大正店</t>
+  </si>
+  <si>
+    <t>焼き鳥・お出汁料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chabo_taisho</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目１７−１６</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
+  </si>
+  <si>
+    <t>参加する</t>
+  </si>
+  <si>
+    <t>三軒家西</t>
+  </si>
+  <si>
+    <t>おばんざい</t>
+  </si>
+  <si>
+    <t>ふじわら君</t>
+  </si>
+  <si>
+    <t>創作料理居酒屋</t>
+  </si>
+  <si>
+    <t>テールブあり</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fujiwarakun_taisho</t>
+  </si>
+  <si>
+    <t>サク飲み</t>
+  </si>
+  <si>
+    <t>テイクアウトOK</t>
+  </si>
+  <si>
+    <t>日曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目１−７</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
+  </si>
+  <si>
+    <t>土日祝は15時～22時</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, d払い、楽天pay、aupay、wesmo</t>
+  </si>
+  <si>
+    <t>はい。希望します。</t>
+  </si>
+  <si>
+    <t>「酔いどれセット」のみで参加</t>
+  </si>
+  <si>
+    <t>大正サロン髭とボヰン</t>
+  </si>
+  <si>
+    <t>立ち飲み・創作料理</t>
+  </si>
+  <si>
+    <t>選べるおばんざい3種セット</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hige_to.boin</t>
+  </si>
+  <si>
+    <t>おばんざい小盛3種+ドリンク1杯</t>
+  </si>
+  <si>
     <t>数種類あるおばんざいから3種類選べます。</t>
   </si>
   <si>
     <t>800円(税込)</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目５−１４</t>
+  </si>
+  <si>
     <t>酔いどれセットの方は０円</t>
   </si>
   <si>
+    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
+  </si>
+  <si>
     <t>おばんざいが無くなるまで。</t>
   </si>
   <si>
-    <t>だしと鶏ちゃぼ大正店</t>
-  </si>
-  <si>
-    <t>焼き鳥・お出汁料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chabo_taisho</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目１７−１６</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
-  </si>
-  <si>
-    <t>ふじわら君</t>
-  </si>
-  <si>
-    <t>創作料理居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/fujiwarakun_taisho</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目１−７</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
-  </si>
-  <si>
-    <t>大正サロン髭とボヰン</t>
-  </si>
-  <si>
-    <t>立ち飲み・創作料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hige_to.boin</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５−１４</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
-  </si>
-  <si>
     <t>大正バル誠~ｓｅｉ~</t>
   </si>
   <si>
@@ -411,115 +411,166 @@
     <t>https://www.instagram.com/izakaya_sei</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目３−１１</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
+  </si>
+  <si>
+    <t>居酒屋たすいち</t>
+  </si>
+  <si>
+    <t>もつ鍋酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_tasuichi</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目８−２３</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
+  </si>
+  <si>
+    <t>地鶏る</t>
+  </si>
+  <si>
+    <t>宮崎鶏の炭火焼き</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jidoru_1013</t>
+  </si>
+  <si>
+    <t>大阪市大正区泉尾３丁目２−７ 1階</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
+  </si>
+  <si>
+    <t>沖縄酒場きじむなーの森</t>
+  </si>
+  <si>
+    <t>沖縄料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目１−１４ タグボート大正 2F</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
+  </si>
+  <si>
     <t>駅前</t>
   </si>
   <si>
     <t>ジビエ肉</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目３−１１</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
-  </si>
-  <si>
     <t>テーブルあり</t>
   </si>
   <si>
+    <t>ナンチャツ亭のエリー</t>
+  </si>
+  <si>
     <t>腹ごしらえ</t>
   </si>
   <si>
-    <t>居酒屋たすいち</t>
-  </si>
-  <si>
-    <t>もつ鍋酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/izakaya_tasuichi</t>
+    <t>昭和レトロなおばんざい</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nanchatteino_erie</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目１７−３３ 平和相互商事大正橋ビル 1F</t>
   </si>
   <si>
     <t>週末延長可能性あり</t>
   </si>
   <si>
+    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
+  </si>
+  <si>
     <t>現金, paypay</t>
   </si>
   <si>
     <t>一品とお酒</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目８−２３</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
+    <t>Neboke-ネボケ</t>
+  </si>
+  <si>
+    <t>隠れ家バー</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Neboke_bar</t>
   </si>
   <si>
     <t>限定30セット / 日</t>
   </si>
   <si>
-    <t>地鶏る</t>
-  </si>
-  <si>
-    <t>宮崎鶏の炭火焼き</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/jidoru_1013</t>
-  </si>
-  <si>
-    <t>大阪市大正区泉尾３丁目２−７ 1階</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
-  </si>
-  <si>
-    <t>沖縄酒場きじむなーの森</t>
-  </si>
-  <si>
-    <t>沖縄料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目１−１４ タグボート大正 2F</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
-  </si>
-  <si>
-    <t>ナンチャツ亭のエリー</t>
-  </si>
-  <si>
-    <t>昭和レトロなおばんざい</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nanchatteino_erie</t>
+    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
+  </si>
+  <si>
+    <t>串焼き酒場ニコヤ</t>
+  </si>
+  <si>
+    <t>創作鉄板串焼き</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicoya1203</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目２５−１０ 1階</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
+  </si>
+  <si>
+    <t>Barカセット</t>
+  </si>
+  <si>
+    <t>80's・ロック・駄菓子</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/showz0069</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目２−５ 1F</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
+  </si>
+  <si>
+    <t>焼肉ホルモンたろちゃん大正橋店</t>
+  </si>
+  <si>
+    <t>駅前で昼から飲める店</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tarochan_taisho</t>
   </si>
   <si>
     <t>クレープ</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目１７−３３ 平和相互商事大正橋ビル 1F</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
-  </si>
-  <si>
     <t>ひと休み</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目２−６</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
+  </si>
+  <si>
     <t>火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
   </si>
   <si>
-    <t>Neboke-ネボケ</t>
-  </si>
-  <si>
     <t>現金</t>
   </si>
   <si>
-    <t>隠れ家バー</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/Neboke_bar</t>
+    <t>鉄板焼き栄八大阪大正店</t>
   </si>
   <si>
     <t>ピロークレープとハンドドリップコーヒー</t>
@@ -528,78 +579,27 @@
     <t>包みタイプのクレープとハンドドリップコーヒーのセットです</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
-  </si>
-  <si>
-    <t>串焼き酒場ニコヤ</t>
-  </si>
-  <si>
-    <t>創作鉄板串焼き</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nicoya1203</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目２５−１０ 1階</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
-  </si>
-  <si>
-    <t>Barカセット</t>
-  </si>
-  <si>
-    <t>80's・ロック・駄菓子</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/showz0069</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目２−５ 1F</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
-  </si>
-  <si>
-    <t>焼肉ホルモンたろちゃん大正橋店</t>
-  </si>
-  <si>
-    <t>駅前で昼から飲める店</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/tarochan_taisho</t>
+    <t>お好み・焼きそば・鉄板居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/teppanyaki_eihachi</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目６−３</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
   </si>
   <si>
     <t>クラスノ</t>
   </si>
   <si>
+    <t>うて食堂 大正BASE</t>
+  </si>
+  <si>
     <t>参加しない</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目２−６</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
-  </si>
-  <si>
-    <t>鉄板焼き栄八大阪大正店</t>
-  </si>
-  <si>
-    <t>お好み・焼きそば・鉄板居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/teppanyaki_eihachi</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目６−３</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
-  </si>
-  <si>
-    <t>うて食堂 大正BASE</t>
-  </si>
-  <si>
     <t>蒸し料理で飲める食堂</t>
   </si>
   <si>
@@ -615,25 +615,37 @@
     <t>ナンチャッ亭のエリー</t>
   </si>
   <si>
+    <t>三軒家東</t>
+  </si>
+  <si>
+    <t>カウンター</t>
+  </si>
+  <si>
+    <t>テイクアウト不可</t>
+  </si>
+  <si>
+    <t>日曜日, 月曜日, 木曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
     <t>大正焼肉ホルモンK2+</t>
   </si>
   <si>
-    <t>三軒家東</t>
-  </si>
-  <si>
     <t>焼肉ホルモン・韓国料理</t>
   </si>
   <si>
     <t>https://www.instagram.com/yakiniku.k2plus</t>
   </si>
   <si>
-    <t>カウンター</t>
-  </si>
-  <si>
-    <t>テイクアウト不可</t>
-  </si>
-  <si>
-    <t>日曜日, 月曜日, 木曜日, 金曜日, 土曜日</t>
+    <t>一休みセット</t>
+  </si>
+  <si>
+    <t>ひと口おばんざいセットと1ドリンク</t>
+  </si>
+  <si>
+    <t>お腹に優しいおばんざいひと口サイズの盛り合わせ</t>
+  </si>
+  <si>
+    <t>限定30</t>
   </si>
   <si>
     <t>大阪市大正区三軒家西１丁目９−３６</t>
@@ -642,12 +654,6 @@
     <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
   </si>
   <si>
-    <t>一休みセット</t>
-  </si>
-  <si>
-    <t>ひと口おばんざいセットと1ドリンク</t>
-  </si>
-  <si>
     <t>呑み処 三日月</t>
   </si>
   <si>
@@ -657,12 +663,6 @@
     <t>https://www.instagram.com/moon.3.3.3</t>
   </si>
   <si>
-    <t>お腹に優しいおばんざいひと口サイズの盛り合わせ</t>
-  </si>
-  <si>
-    <t>限定30</t>
-  </si>
-  <si>
     <t>大阪市大正区三軒家東１丁目４−８</t>
   </si>
   <si>
@@ -675,6 +675,12 @@
     <t>https://www.instagram.com/ebisuya.taisyo</t>
   </si>
   <si>
+    <t>バーガー酒場「ハンバーガー・ママ」</t>
+  </si>
+  <si>
+    <t>ハンバーガー</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家東１丁目５－１０</t>
   </si>
   <si>
@@ -684,15 +690,33 @@
     <t>海鮮居酒屋</t>
   </si>
   <si>
+    <t>月曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
     <t>https://www.instagram.com/sanchan.o2</t>
   </si>
   <si>
+    <t>火・木は18:00オープン</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, 各種QR決済</t>
+  </si>
+  <si>
+    <t>どれクエII限定ミニバーガー＋ドリンクセット</t>
+  </si>
+  <si>
+    <t>イベント期間限定ミニバーガー＋ちょいポテト＋1ドリンク</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家西１丁目１７−２０</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
   </si>
   <si>
+    <t>1,000円</t>
+  </si>
+  <si>
     <t>SoundBar花いち</t>
   </si>
   <si>
@@ -702,21 +726,12 @@
     <t>https://www.instagram.com/soundbar__hanaichi</t>
   </si>
   <si>
-    <t>バーガー酒場「ハンバーガー・ママ」</t>
-  </si>
-  <si>
-    <t>ハンバーガー</t>
-  </si>
-  <si>
     <t>大阪市大正区三軒家東１丁目５−１４ 2階</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
   </si>
   <si>
-    <t>月曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
-  </si>
-  <si>
     <t>ザ·沖縄</t>
   </si>
   <si>
@@ -726,22 +741,10 @@
     <t>https://www.instagram.com/za.okinawa</t>
   </si>
   <si>
-    <t>火・木は18:00オープン</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード, 各種QR決済</t>
-  </si>
-  <si>
-    <t>どれクエII限定ミニバーガー＋ドリンクセット</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/Prnu5oBX6hyQzpft6</t>
   </si>
   <si>
-    <t>イベント期間限定ミニバーガー＋ちょいポテト＋1ドリンク</t>
-  </si>
-  <si>
-    <t>1,000円</t>
+    <t>BARカセット</t>
   </si>
   <si>
     <t>NONA</t>
@@ -751,6 +754,12 @@
   </si>
   <si>
     <t>https://www.instagram.com/cafe.bar.nona9</t>
+  </si>
+  <si>
+    <t>BAR</t>
+  </si>
+  <si>
+    <t>夜遊び</t>
   </si>
   <si>
     <t>大阪市大正区泉尾２丁目１１−９</t>
@@ -767,6 +776,12 @@
     </r>
   </si>
   <si>
+    <t>全て</t>
+  </si>
+  <si>
+    <t>店舗STAFFのシフトにより若干の時間変動あり</t>
+  </si>
+  <si>
     <t>魚と沖縄料理 えっせんす</t>
   </si>
   <si>
@@ -776,10 +791,13 @@
     <t>https://www.instagram.com/essence_taishou</t>
   </si>
   <si>
-    <t>BARカセット</t>
-  </si>
-  <si>
-    <t>BAR</t>
+    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
+  </si>
+  <si>
+    <t>ぐんたいガニ捕獲セット（カニぱん）</t>
+  </si>
+  <si>
+    <t>ドリンクを注文したお客様に三立製菓さんの「かにパン」をプレゼント！</t>
   </si>
   <si>
     <t>大阪市大正区泉尾３丁目１２−１７ 泉尾商店 街内</t>
@@ -788,10 +806,16 @@
     <t>https://maps.app.goo.gl/NL1uEH8kq3MhMEzdA</t>
   </si>
   <si>
-    <t>夜遊び</t>
-  </si>
-  <si>
-    <t>全て</t>
+    <t>店頭で捕獲したぐんたいガ二（かにパン）は、その場で食べても良し！持ち帰って、明日のパンにしても良し！</t>
+  </si>
+  <si>
+    <t>1000円</t>
+  </si>
+  <si>
+    <t>500円</t>
+  </si>
+  <si>
+    <t>30セット予定（好評の場合追加有り）</t>
   </si>
   <si>
     <t>Bar Coco-Color</t>
@@ -803,19 +827,16 @@
     <t>https://www.instagram.com/bar_cococolor_taisho</t>
   </si>
   <si>
-    <t>店舗STAFFのシフトにより若干の時間変動あり</t>
-  </si>
-  <si>
-    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
-  </si>
-  <si>
-    <t>ぐんたいガニ捕獲セット（カニぱん）</t>
-  </si>
-  <si>
-    <t>ドリンクを注文したお客様に三立製菓さんの「かにパン」をプレゼント！</t>
-  </si>
-  <si>
-    <t>店頭で捕獲したぐんたいガ二（かにパン）は、その場で食べても良し！持ち帰って、明日のパンにしても良し！</t>
+    <t>ぐんたいガニ乱獲クエスト</t>
+  </si>
+  <si>
+    <t>追加ドリンクを注文して頂いたお客様に「勇者のサイコロ」でSTAFFに挑戦して貰います。見事STAFFに勝利したお客様には三立製菓さんの「かにビス」をプレゼント！</t>
+  </si>
+  <si>
+    <t>追加ドリンクの料金500円～900円（スコッチは除く）</t>
+  </si>
+  <si>
+    <t>追加ドリンクの料金のみ</t>
   </si>
   <si>
     <t>大阪市大正区三軒家西１丁目１６−１６</t>
@@ -824,27 +845,6 @@
     <t>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</t>
   </si>
   <si>
-    <t>1000円</t>
-  </si>
-  <si>
-    <t>500円</t>
-  </si>
-  <si>
-    <t>30セット予定（好評の場合追加有り）</t>
-  </si>
-  <si>
-    <t>ぐんたいガニ乱獲クエスト</t>
-  </si>
-  <si>
-    <t>追加ドリンクを注文して頂いたお客様に「勇者のサイコロ」でSTAFFに挑戦して貰います。見事STAFFに勝利したお客様には三立製菓さんの「かにビス」をプレゼント！</t>
-  </si>
-  <si>
-    <t>追加ドリンクの料金500円～900円（スコッチは除く）</t>
-  </si>
-  <si>
-    <t>追加ドリンクの料金のみ</t>
-  </si>
-  <si>
     <t>2酔いどれセットご注文、又は2杯目以降のご注文から挑戦して頂けます</t>
   </si>
   <si>
@@ -863,7 +863,7 @@
     <t>https://maps.app.goo.gl/PB2QxJm3seTe8PFH6</t>
   </si>
   <si>
-    <t>TM's DINER</t>
+    <t>TM’s DINER</t>
   </si>
   <si>
     <t>イタリアン・メキシカン・アメリカン</t>
@@ -899,12 +899,12 @@
     <t>隠れ家的なお好み焼き</t>
   </si>
   <si>
+    <t>https://www.instagram.com/okonomiyaki_mamama15</t>
+  </si>
+  <si>
     <t>いいえ、希望しません。</t>
   </si>
   <si>
-    <t>https://www.instagram.com/okonomiyaki_mamama15</t>
-  </si>
-  <si>
     <t>1000円セット</t>
   </si>
   <si>
@@ -935,7 +935,7 @@
     <t>https://www.instagram.com/__2knme0703</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2A</t>
+    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正</t>
   </si>
   <si>
     <t>Fine</t>
@@ -957,9 +957,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/bar_edit_osaka</t>
-  </si>
-  <si>
-    <t>その日の状況により早く閉める場合あり。</t>
   </si>
   <si>
     <t>大阪市大正区泉尾１丁目３０−１５ 平本ビル</t>
@@ -976,6 +973,18 @@
     </r>
   </si>
   <si>
+    <t>その日の状況により早く閉める場合あり。</t>
+  </si>
+  <si>
+    <t>うおしんのご愛嬌</t>
+  </si>
+  <si>
+    <t>中央市場の魚屋さんが運営する居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/uoshin_no_goaikyou</t>
+  </si>
+  <si>
     <t>花いちオリジナルセット</t>
   </si>
   <si>
@@ -986,21 +995,6 @@
   </si>
   <si>
     <t>なし</t>
-  </si>
-  <si>
-    <t>うおしんのご愛嬌</t>
-  </si>
-  <si>
-    <t>中央市場の魚屋さんが運営する居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/uoshin_no_goaikyou</t>
-  </si>
-  <si>
-    <t>カラオケで95点以上にチャレンジ！！</t>
-  </si>
-  <si>
-    <t>カラオケで95点以上出した方に、〆のカップ麺1個プレゼント！！</t>
   </si>
   <si>
     <r>
@@ -1014,6 +1008,12 @@
     </r>
   </si>
   <si>
+    <t>カラオケで95点以上にチャレンジ！！</t>
+  </si>
+  <si>
+    <t>カラオケで95点以上出した方に、〆のカップ麺1個プレゼント！！</t>
+  </si>
+  <si>
     <t>9回の表</t>
   </si>
   <si>
@@ -1060,28 +1060,22 @@
     </r>
   </si>
   <si>
+    <t>鉄板焼き ぷれこ</t>
+  </si>
+  <si>
+    <t>変態植物倶楽部の店</t>
+  </si>
+  <si>
     <t>居酒屋</t>
   </si>
   <si>
-    <t>鉄板焼き ぷれこ</t>
-  </si>
-  <si>
-    <t>変態植物倶楽部の店</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/pureko.yakisoba___</t>
   </si>
   <si>
+    <t>大阪市大正区泉尾１丁目２２−１２</t>
+  </si>
+  <si>
     <t>22時以降も席とお店が開いていればOK</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード</t>
-  </si>
-  <si>
-    <t>誠seiセット</t>
-  </si>
-  <si>
-    <t>大阪市大正区泉尾１丁目２２−１２</t>
   </si>
   <si>
     <r>
@@ -1095,6 +1089,12 @@
     </r>
   </si>
   <si>
+    <t>現金, paypay, クレジットカード</t>
+  </si>
+  <si>
+    <t>誠seiセット</t>
+  </si>
+  <si>
     <t>ワンドリンク＋串カツ５本or牡蠣セット</t>
   </si>
   <si>
@@ -1160,6 +1160,15 @@
     </r>
   </si>
   <si>
+    <t>元気玉セット</t>
+  </si>
+  <si>
+    <t>元気玉+黒糖焼酎（じょうご）一杯</t>
+  </si>
+  <si>
+    <t>未定</t>
+  </si>
+  <si>
     <t>酒と魚 喰海~KUKAI~</t>
   </si>
   <si>
@@ -1167,12 +1176,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/kukai_izakaya_</t>
-  </si>
-  <si>
-    <t>元気玉セット</t>
-  </si>
-  <si>
-    <t>元気玉+黒糖焼酎（じょうご）一杯</t>
   </si>
   <si>
     <t>大阪市大正区千島３丁目３−１２ シティハイツ大正</t>
@@ -1189,7 +1192,22 @@
     </r>
   </si>
   <si>
-    <t>未定</t>
+    <t>焼肉・ホルモン</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, 電子マネー</t>
+  </si>
+  <si>
+    <t>選べる名物厚切り肉！</t>
+  </si>
+  <si>
+    <t>好きなドリンク1杯と名物の厚切り上塩タンか厚切り特上ハラミどちらかを選んでもらえるセット</t>
+  </si>
+  <si>
+    <t>酔いどれセットのテイクアウト不可</t>
+  </si>
+  <si>
+    <t>2,000円</t>
   </si>
   <si>
     <t>Zakky's ホットドッグ</t>
@@ -1198,7 +1216,22 @@
     <t>大正アメリンカンダイナー</t>
   </si>
   <si>
+    <t>0円</t>
+  </si>
+  <si>
     <t>https://www.instagram.com/zakkys_hotdog</t>
+  </si>
+  <si>
+    <t>期間中いつでも可</t>
+  </si>
+  <si>
+    <t>ピンゾロチャレンジ</t>
+  </si>
+  <si>
+    <t>サイコロで1のゾロ目が出たら酔いどれセットが半額になる</t>
+  </si>
+  <si>
+    <t>10個</t>
   </si>
   <si>
     <t>大阪市大正区千島３丁目１２−１３ ハイグレード千島</t>
@@ -1261,9 +1294,6 @@
     </r>
   </si>
   <si>
-    <t>焼肉・ホルモン</t>
-  </si>
-  <si>
     <t>3PIECE</t>
   </si>
   <si>
@@ -1273,7 +1303,13 @@
     <t>https://www.instagram.com/3piece_osake</t>
   </si>
   <si>
-    <t>現金, paypay, クレジットカード, 電子マネー</t>
+    <t>3:30飲み放題ラストオーダー、4:30で終了、退店</t>
+  </si>
+  <si>
+    <t>現金, クレジットカード, Paypay、D払い以外のバーコード決済</t>
+  </si>
+  <si>
+    <t>1H飲み放題1000円</t>
   </si>
   <si>
     <t>大阪市大正区南恩加島６丁目７−８</t>
@@ -1290,22 +1326,10 @@
     </r>
   </si>
   <si>
-    <t>選べる名物厚切り肉！</t>
-  </si>
-  <si>
-    <t>好きなドリンク1杯と名物の厚切り上塩タンか厚切り特上ハラミどちらかを選んでもらえるセット</t>
-  </si>
-  <si>
-    <t>酔いどれセットのテイクアウト不可</t>
-  </si>
-  <si>
-    <t>2,000円</t>
-  </si>
-  <si>
-    <t>0円</t>
-  </si>
-  <si>
-    <t>期間中いつでも可</t>
+    <t>1H飲み放題1000円(チャージ料込み)</t>
+  </si>
+  <si>
+    <t>ラストオーダー15分前、入店3:30まで</t>
   </si>
   <si>
     <t>たこ焼き･お好み焼き そーすや</t>
@@ -1315,15 +1339,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/so__suya</t>
-  </si>
-  <si>
-    <t>ピンゾロチャレンジ</t>
-  </si>
-  <si>
-    <t>サイコロで1のゾロ目が出たら酔いどれセットが半額になる</t>
-  </si>
-  <si>
-    <t>10個</t>
   </si>
   <si>
     <t>大阪市大正区鶴町３丁目９−８</t>
@@ -1377,28 +1392,16 @@
     </r>
   </si>
   <si>
+    <t>泉尾</t>
+  </si>
+  <si>
     <t>いっぱい呑み 花</t>
   </si>
   <si>
     <t>https://www.instagram.com/ippainomi.hana0806</t>
   </si>
   <si>
-    <t>3:30飲み放題ラストオーダー、4:30で終了、退店</t>
-  </si>
-  <si>
-    <t>現金, クレジットカード, Paypay、D払い以外のバーコード決済</t>
-  </si>
-  <si>
-    <t>1H飲み放題1000円</t>
-  </si>
-  <si>
-    <t>1H飲み放題1000円(チャージ料込み)</t>
-  </si>
-  <si>
     <t>大阪市大正区千島3丁目4-7</t>
-  </si>
-  <si>
-    <t>ラストオーダー15分前、入店3:30まで</t>
   </si>
   <si>
     <r>
@@ -1418,7 +1421,16 @@
     <t>https://www.instagram.com/tanom_cafe</t>
   </si>
   <si>
+    <t>ドラクエ限定　一杯目100円</t>
+  </si>
+  <si>
+    <t>入店1杯目100円</t>
+  </si>
+  <si>
     <t>大阪市大正区泉尾１丁目１３−１５</t>
+  </si>
+  <si>
+    <t>無し</t>
   </si>
   <si>
     <r>
@@ -1432,66 +1444,54 @@
     </r>
   </si>
   <si>
+    <t>立体四目並べ　勝てば、1杯無料</t>
+  </si>
+  <si>
+    <t>勝てば1杯無料</t>
+  </si>
+  <si>
+    <t>100円</t>
+  </si>
+  <si>
+    <t>スパイスカレー</t>
+  </si>
+  <si>
+    <t>昼飲み</t>
+  </si>
+  <si>
+    <t>土曜日</t>
+  </si>
+  <si>
+    <t>15時ラストオーダー　15時30分クローズ</t>
+  </si>
+  <si>
     <t>焼く鳥屋 おかもと 大正店</t>
   </si>
   <si>
     <t>https://www.instagram.com/yakutori_taisho</t>
   </si>
   <si>
+    <t>酔いどれカレー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">チキンスパイスカレー小 </t>
+  </si>
+  <si>
+    <t>800円</t>
+  </si>
+  <si>
+    <t>カレーがなくなり次第終了</t>
+  </si>
+  <si>
+    <t>激辛スパイスカレー 4辛</t>
+  </si>
+  <si>
     <t>立ち飲み処 雄</t>
   </si>
   <si>
     <t>https://www.instagram.com/you_taisho</t>
   </si>
   <si>
-    <t>泉尾</t>
-  </si>
-  <si>
-    <t>ドラクエ限定　一杯目100円</t>
-  </si>
-  <si>
-    <t>入店1杯目100円</t>
-  </si>
-  <si>
-    <t>無し</t>
-  </si>
-  <si>
-    <t>立体四目並べ　勝てば、1杯無料</t>
-  </si>
-  <si>
-    <t>勝てば1杯無料</t>
-  </si>
-  <si>
-    <t>100円</t>
-  </si>
-  <si>
-    <t>スパイスカレー</t>
-  </si>
-  <si>
-    <t>昼飲み</t>
-  </si>
-  <si>
-    <t>土曜日</t>
-  </si>
-  <si>
-    <t>15時ラストオーダー　15時30分クローズ</t>
-  </si>
-  <si>
-    <t>酔いどれカレー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">チキンスパイスカレー小 </t>
-  </si>
-  <si>
-    <t>800円</t>
-  </si>
-  <si>
-    <t>カレーがなくなり次第終了</t>
-  </si>
-  <si>
-    <t>激辛スパイスカレー 4辛</t>
-  </si>
-  <si>
     <t>4辛のスパイスカレー食べ切ったら、次回スパイスカレー400円引き</t>
   </si>
   <si>
@@ -1568,6 +1568,94 @@
   </si>
   <si>
     <t>ワンドリンク込み</t>
+  </si>
+  <si>
+    <t>串焼き・鉄板焼き</t>
+  </si>
+  <si>
+    <t>日曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
+    <t>鉄板焼2種盛合せ</t>
+  </si>
+  <si>
+    <t>鉄板焼おつまみ2種</t>
+  </si>
+  <si>
+    <t>仕入状況により内容変わりますので詳しくは記載せずにいます</t>
+  </si>
+  <si>
+    <t>多国籍料理</t>
+  </si>
+  <si>
+    <t>日曜日, 月曜日, 火曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
+    <t>ディナーは30分前ラストオーダーなのでそれまでにご来店をお願いします。</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, d払い、auペイ、楽天ペイ、メルペイ、などなど</t>
+  </si>
+  <si>
+    <t>TM's酔いどれセット</t>
+  </si>
+  <si>
+    <t>イベント限定メニュー+1ドリンク</t>
+  </si>
+  <si>
+    <t>南恩加島</t>
+  </si>
+  <si>
+    <t>金曜、土曜力尽きるまで</t>
+  </si>
+  <si>
+    <t>カラオケで高得点！</t>
+  </si>
+  <si>
+    <t>93点以上だした方は指定ドリンク一杯無料</t>
+  </si>
+  <si>
+    <t>？</t>
+  </si>
+  <si>
+    <t>鶏料理</t>
+  </si>
+  <si>
+    <t>月曜日, 火曜日, 水曜日, 木曜日</t>
+  </si>
+  <si>
+    <t>現金, クレジットカード</t>
+  </si>
+  <si>
+    <t>ドリンク1杯、肉豆腐、国産鶏の出汁煮2本</t>
+  </si>
+  <si>
+    <t>ドリンクは瓶ビール、日本酒を除く</t>
+  </si>
+  <si>
+    <t>1100円(税込)</t>
+  </si>
+  <si>
+    <t>鉄板焼・焼きそば</t>
+  </si>
+  <si>
+    <t>とん平＆ドリンク</t>
+  </si>
+  <si>
+    <t>とん平とドリンク(生・酎ハイ・ハイボール)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　
+</t>
+  </si>
+  <si>
+    <t>限定なし</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>おまかせします</t>
   </si>
 </sst>
 </file>
@@ -1577,7 +1665,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1633,6 +1721,11 @@
       <color rgb="FF467886"/>
       <name val="&quot;Meiryo UI&quot;"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1662,7 +1755,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1699,6 +1792,9 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1707,9 +1803,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="19" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1723,17 +1816,23 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1818,8 +1917,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AQ21" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$AQ$21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AQ26" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$AQ$26"/>
   <tableColumns count="43">
     <tableColumn name="タイムスタンプ" id="1"/>
     <tableColumn name="店名" id="2"/>
@@ -2075,123 +2174,127 @@
     <col customWidth="1" min="3" max="3" width="20.0"/>
     <col customWidth="1" min="4" max="14" width="18.88"/>
     <col customWidth="1" min="15" max="15" width="43.75"/>
-    <col customWidth="1" min="16" max="43" width="18.88"/>
+    <col customWidth="1" min="16" max="32" width="18.88"/>
+    <col customWidth="1" min="33" max="33" width="33.63"/>
+    <col customWidth="1" min="34" max="34" width="66.25"/>
+    <col customWidth="1" min="35" max="35" width="39.13"/>
+    <col customWidth="1" min="36" max="43" width="18.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AG1" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="AH1" s="8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="AI1" s="8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="AJ1" s="8" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="AK1" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="AL1" s="9" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AM1" s="10" t="s">
         <v>0</v>
@@ -2210,68 +2313,68 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="12">
+      <c r="A2" s="13">
         <v>46280.631479247684</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="14">
+      <c r="C2" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="15">
         <v>0.7083333333357587</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="15">
         <v>0.9166666666642413</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P2" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="R2" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="U2" s="13" t="s">
-        <v>105</v>
+      <c r="L2" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="AM2" s="16">
         <f t="array" ref="AM2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -2295,67 +2398,67 @@
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>46291.663153263886</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J3" s="14">
+      <c r="B3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="15">
         <v>0.20833333333575865</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="15">
         <v>0.45833333333575865</v>
       </c>
-      <c r="L3" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="R3" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="S3" s="13">
+      <c r="L3" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="M3" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="R3" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="S3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="T3" s="13">
+      <c r="T3" s="14">
         <v>0.0</v>
       </c>
-      <c r="U3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="AL3" s="13">
+      <c r="U3" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL3" s="14">
         <v>30.0</v>
       </c>
       <c r="AM3" s="16">
@@ -2380,61 +2483,61 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>46292.641919664355</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="J4" s="14">
+      <c r="B4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="15">
         <v>0.7916666666642413</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="15">
         <v>0.9375</v>
       </c>
-      <c r="M4" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N4" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="S4" s="13">
+      <c r="M4" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="S4" s="14">
         <v>1000.0</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="14">
         <v>0.0</v>
       </c>
-      <c r="AL4" s="13">
+      <c r="AL4" s="14">
         <v>10.0</v>
       </c>
       <c r="AM4" s="16">
@@ -2459,14 +2562,14 @@
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>46295.48182782407</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>178</v>
+      <c r="B5" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="AM5" s="16" t="str">
         <f t="array" ref="AM5">_xlfn.XLOOKUP($B5,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -2490,67 +2593,67 @@
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>46295.488864942134</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="J6" s="14">
+      <c r="G6" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="J6" s="15">
         <v>0.7291666666642413</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="15">
         <v>0.9583333333357587</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P6" s="13" t="s">
+      <c r="M6" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="R6" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="S6" s="14">
+        <v>800.0</v>
+      </c>
+      <c r="T6" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="U6" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="R6" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="S6" s="13">
-        <v>800.0</v>
-      </c>
-      <c r="T6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="U6" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL6" s="13">
+      <c r="AL6" s="14">
         <v>30.0</v>
       </c>
       <c r="AM6" s="16">
@@ -2575,64 +2678,64 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>46295.56995630787</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="Q7" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I7" s="13" t="s">
+      <c r="S7" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="J7" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="14">
+      <c r="T7" s="14">
         <v>0.0</v>
       </c>
-      <c r="L7" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="T7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AL7" s="13">
+      <c r="AL7" s="14">
         <v>20.0</v>
       </c>
       <c r="AM7" s="16" t="str">
@@ -2657,85 +2760,85 @@
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>46295.62130144676</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="J8" s="15">
+        <v>0.875</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.125</v>
+      </c>
+      <c r="L8" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I8" s="13" t="s">
+      <c r="M8" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="J8" s="14">
-        <v>0.875</v>
-      </c>
-      <c r="K8" s="14">
-        <v>0.125</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="13" t="s">
+      <c r="AA8" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB8" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="AC8" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="AA8" s="13" t="s">
+      <c r="AD8" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="AB8" s="13" t="s">
+      <c r="AE8" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="AC8" s="13" t="s">
+      <c r="AF8" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="AD8" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="AE8" s="13" t="s">
+      <c r="AG8" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="AF8" s="13" t="s">
+      <c r="AH8" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="AG8" s="13" t="s">
+      <c r="AI8" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AH8" s="13" t="s">
+      <c r="AJ8" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AI8" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="AJ8" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="AK8" s="13" t="s">
+      <c r="AK8" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AL8" s="14">
         <v>15.0</v>
       </c>
       <c r="AM8" s="16">
@@ -2760,58 +2863,58 @@
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>46295.810687523146</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="J9" s="14">
+      <c r="B9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J9" s="15">
         <v>0.8333333333357587</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="15">
         <v>0.125</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" s="13" t="s">
+      <c r="M9" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P9" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="Q9" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="S9" s="13">
+      <c r="S9" s="14">
         <v>1000.0</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AL9" s="14">
         <v>5.0</v>
       </c>
       <c r="AM9" s="16">
@@ -2836,82 +2939,82 @@
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>46295.91687133102</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="13" t="s">
+      <c r="B10" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0.875</v>
+      </c>
+      <c r="K10" s="15">
+        <v>0.08333333333575865</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O10" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="J10" s="14">
-        <v>0.875</v>
-      </c>
-      <c r="K10" s="14">
-        <v>0.08333333333575865</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA10" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="AB10" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="AC10" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="AD10" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="AE10" s="13" t="s">
+      <c r="AA10" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="AF10" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="AG10" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="AH10" s="13" t="s">
+      <c r="AB10" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="AC10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD10" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE10" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="AG10" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="AI10" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AJ10" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AL10" s="13">
+      <c r="AH10" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI10" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ10" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL10" s="14">
         <v>5.0</v>
       </c>
       <c r="AM10" s="16">
@@ -2936,61 +3039,61 @@
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>46296.49762741898</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="J11" s="14">
+      <c r="C11" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J11" s="15">
         <v>0.75</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="15">
         <v>0.9166666666642413</v>
       </c>
-      <c r="L11" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="M11" s="13" t="s">
+      <c r="L11" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="N11" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q11" s="13" t="s">
+      <c r="M11" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q11" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="14">
         <v>1000.0</v>
       </c>
-      <c r="AL11" s="13">
+      <c r="AL11" s="14">
         <v>10.0</v>
       </c>
       <c r="AM11" s="16">
@@ -3015,70 +3118,70 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>46296.538205590274</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="B12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="G12" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J12" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="K12" s="15">
+        <v>0.9166666666642413</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O12" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="J12" s="14">
-        <v>0.625</v>
-      </c>
-      <c r="K12" s="14">
-        <v>0.9166666666642413</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA12" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="AB12" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="AD12" s="13">
+      <c r="AA12" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="AB12" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="AD12" s="14">
         <v>1000.0</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AE12" s="14">
         <v>330.0</v>
       </c>
-      <c r="AG12" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="AH12" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="AI12" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="AL12" s="13">
+      <c r="AG12" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AH12" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AI12" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AL12" s="14">
         <v>10.0</v>
       </c>
       <c r="AM12" s="16">
@@ -3103,77 +3206,77 @@
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>46296.62372876157</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="C13" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J13" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0.9166666666642413</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="J13" s="14">
-        <v>0.625</v>
-      </c>
-      <c r="K13" s="14">
-        <v>0.9166666666642413</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA13" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="AB13" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="AC13" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="AD13" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="AE13" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="AF13" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="AG13" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="AH13" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="AI13" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="AL13" s="13" t="s">
-        <v>396</v>
+      <c r="AA13" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="AB13" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="AC13" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="AD13" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="AE13" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="AF13" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="AG13" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="AH13" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="AI13" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="AL13" s="14" t="s">
+        <v>376</v>
       </c>
       <c r="AM13" s="16">
         <f t="array" ref="AM13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3197,64 +3300,64 @@
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>46300.61462475694</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="J14" s="14">
+      <c r="B14" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="15">
         <v>0.8333333333357587</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="15">
         <v>0.14583333333575865</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="R14" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="S14" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="AL14" s="13">
+      <c r="L14" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="S14" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AL14" s="14">
         <v>15.0</v>
       </c>
       <c r="AM14" s="16">
@@ -3279,76 +3382,76 @@
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>46304.76113125</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0.9930555555547471</v>
+      </c>
+      <c r="M15" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA15" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB15" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="AD15" s="14">
+        <v>100.0</v>
+      </c>
+      <c r="AE15" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AF15" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="AG15" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="J15" s="14">
-        <v>0.8125</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0.9930555555547471</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA15" s="13" t="s">
+      <c r="AH15" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="AB15" s="13" t="s">
+      <c r="AI15" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="AD15" s="13">
-        <v>100.0</v>
-      </c>
-      <c r="AE15" s="13">
+      <c r="AJ15" s="14">
         <v>0.0</v>
       </c>
-      <c r="AF15" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="AG15" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="AH15" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="AI15" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="AJ15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="AL15" s="13">
+      <c r="AL15" s="14">
         <v>20.0</v>
       </c>
       <c r="AM15" s="16">
@@ -3373,76 +3476,76 @@
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>46304.852581238425</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" s="13" t="s">
+      <c r="C16" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="J16" s="15">
+        <v>0.47916666666424135</v>
+      </c>
+      <c r="K16" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA16" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="J16" s="14">
-        <v>0.47916666666424135</v>
-      </c>
-      <c r="K16" s="14">
-        <v>0.625</v>
-      </c>
-      <c r="L16" s="13" t="s">
+      <c r="AB16" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA16" s="13" t="s">
+      <c r="AD16" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="AB16" s="13" t="s">
+      <c r="AF16" s="14" t="s">
         <v>435</v>
       </c>
-      <c r="AD16" s="13" t="s">
+      <c r="AG16" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="AF16" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="AG16" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="AH16" s="13" t="s">
+      <c r="AH16" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="AI16" s="13" t="s">
+      <c r="AI16" s="14" t="s">
         <v>440</v>
       </c>
-      <c r="AK16" s="13" t="s">
+      <c r="AK16" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="AL16" s="13" t="s">
+      <c r="AL16" s="14" t="s">
         <v>442</v>
       </c>
       <c r="AM16" s="16">
@@ -3467,58 +3570,58 @@
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>46305.67339996528</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F17" s="13" t="s">
+      <c r="C17" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="F17" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="13" t="s">
+      <c r="G17" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="15">
         <v>0.7083333333357587</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="15">
         <v>0.8958333333357587</v>
       </c>
-      <c r="M17" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="P17" s="13" t="s">
+      <c r="M17" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P17" s="14" t="s">
         <v>446</v>
       </c>
-      <c r="Q17" s="13" t="s">
+      <c r="Q17" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="S17" s="13" t="s">
+      <c r="S17" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="AL17" s="13">
+      <c r="AL17" s="14">
         <v>10.0</v>
       </c>
       <c r="AM17" s="16">
@@ -3543,67 +3646,67 @@
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>46305.71587197916</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="13" t="s">
+      <c r="C18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="15">
         <v>0.7708333333357587</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="15">
         <v>0.9166666666642413</v>
       </c>
-      <c r="M18" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA18" s="13" t="s">
+      <c r="M18" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA18" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="AB18" s="13" t="s">
+      <c r="AB18" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AD18" s="14">
         <v>500.0</v>
       </c>
-      <c r="AG18" s="13" t="s">
+      <c r="AG18" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="AH18" s="13" t="s">
+      <c r="AH18" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="AI18" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="AL18" s="13">
+      <c r="AI18" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="AL18" s="14">
         <v>10.0</v>
       </c>
       <c r="AM18" s="16">
@@ -3628,68 +3731,68 @@
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>46305.73525341435</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="B19" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J19" s="14">
+      <c r="E19" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="15">
         <v>0.7083333333357587</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="15">
         <v>0.875</v>
       </c>
-      <c r="M19" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA19" s="13" t="s">
+      <c r="M19" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA19" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="AB19" s="13" t="s">
+      <c r="AB19" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="14">
         <v>1000.0</v>
       </c>
-      <c r="AG19" s="13" t="s">
+      <c r="AG19" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="AH19" s="13" t="s">
+      <c r="AH19" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="AI19" s="13">
+      <c r="AI19" s="14">
         <v>100.0</v>
       </c>
-      <c r="AL19" s="13" t="s">
-        <v>396</v>
+      <c r="AL19" s="14">
+        <v>10.0</v>
       </c>
       <c r="AM19" s="16">
         <f t="array" ref="AM19">_xlfn.XLOOKUP($B19,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3713,61 +3816,61 @@
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>46305.85531787037</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="13" t="s">
+      <c r="C20" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J20" s="14">
+      <c r="F20" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="J20" s="15">
         <v>0.8333333333357587</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="15">
         <v>0.9583333333357587</v>
       </c>
-      <c r="M20" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="O20" s="13" t="s">
+      <c r="M20" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O20" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="V20" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="W20" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="X20" s="13" t="s">
+      <c r="X20" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="Y20" s="13" t="s">
+      <c r="Y20" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="AL20" s="13">
+      <c r="AL20" s="14">
         <v>2.0</v>
       </c>
       <c r="AM20" s="16">
@@ -3784,7 +3887,7 @@
       </c>
       <c r="AP20" s="16" t="str">
         <f t="array" ref="AP20">_xlfn.XLOOKUP($B20,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
-        <v>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2A</v>
+        <v>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正</v>
       </c>
       <c r="AQ20" s="16" t="str">
         <f t="array" ref="AQ20">_xlfn.XLOOKUP($B20,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
@@ -3792,14 +3895,14 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>46306.81166831018</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>178</v>
+      <c r="B21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>186</v>
       </c>
       <c r="AM21" s="16">
         <f t="array" ref="AM21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3820,6 +3923,440 @@
       <c r="AQ21" s="17" t="str">
         <f t="array" ref="AQ21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="13">
+        <v>46309.79352489584</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="J22" s="15">
+        <v>0.7083333333357587</v>
+      </c>
+      <c r="K22" s="15">
+        <v>0.9166666666642413</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P22" s="14" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q22" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="S22" s="14">
+        <v>1000.0</v>
+      </c>
+      <c r="T22" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL22" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="AM22" s="24">
+        <f t="array" ref="AM22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="AN22" s="24" t="str">
+        <f t="array" ref="AN22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>お好み・焼きそば・鉄板居酒屋</v>
+      </c>
+      <c r="AO22" s="25" t="str">
+        <f t="array" ref="AO22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/teppanyaki_eihachi</v>
+      </c>
+      <c r="AP22" s="24" t="str">
+        <f t="array" ref="AP22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区三軒家西１丁目６−３</v>
+      </c>
+      <c r="AQ22" s="25" t="str">
+        <f t="array" ref="AQ22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="13">
+        <v>46310.973587430555</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="J23" s="15">
+        <v>0.47916666666424135</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="N23" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O23" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q23" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="U23" s="14">
+        <v>30.0</v>
+      </c>
+      <c r="AL23" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="AM23" s="24">
+        <f t="array" ref="AM23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>32</v>
+      </c>
+      <c r="AN23" s="24" t="str">
+        <f t="array" ref="AN23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>イタリアン・メキシカン・アメリカン</v>
+      </c>
+      <c r="AO23" s="25" t="str">
+        <f t="array" ref="AO23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/tms_diner_osaka</v>
+      </c>
+      <c r="AP23" s="24" t="str">
+        <f t="array" ref="AP23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区三軒家東１丁目２−５ 2F</v>
+      </c>
+      <c r="AQ23" s="25" t="str">
+        <f t="array" ref="AQ23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/qM8P7SU6UqcARZm29</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="13">
+        <v>46312.58616018519</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="15">
+        <v>0.7916666666642413</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="V24" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="W24" s="14" t="s">
+        <v>479</v>
+      </c>
+      <c r="X24" s="14">
+        <v>100.0</v>
+      </c>
+      <c r="Y24" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="AL24" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="AM24" s="24">
+        <f t="array" ref="AM24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>53</v>
+      </c>
+      <c r="AN24" s="24" t="str">
+        <f t="array" ref="AN24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>アットホームなカラオケBAR</v>
+      </c>
+      <c r="AO24" s="25" t="str">
+        <f t="array" ref="AO24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/3piece_osake</v>
+      </c>
+      <c r="AP24" s="24" t="str">
+        <f t="array" ref="AP24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区南恩加島６丁目７−８</v>
+      </c>
+      <c r="AQ24" s="25" t="str">
+        <f t="array" ref="AQ24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/67gvLqPdoESWNqod7</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="13">
+        <v>46315.68812100694</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="J25" s="15">
+        <v>0.7291666666642413</v>
+      </c>
+      <c r="K25" s="15">
+        <v>0.9583333333357587</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="O25" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="R25" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="S25" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="U25" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AL25" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="AM25" s="24">
+        <f t="array" ref="AM25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>9</v>
+      </c>
+      <c r="AN25" s="24" t="str">
+        <f t="array" ref="AN25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>焼き鳥・お出汁料理</v>
+      </c>
+      <c r="AO25" s="25" t="str">
+        <f t="array" ref="AO25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/chabo_taisho</v>
+      </c>
+      <c r="AP25" s="24" t="str">
+        <f t="array" ref="AP25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区三軒家東１丁目１７−１６</v>
+      </c>
+      <c r="AQ25" s="25" t="str">
+        <f t="array" ref="AQ25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="13">
+        <v>46315.72136438657</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.7083333333357587</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.41666666666424135</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="O26" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA26" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="AB26" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="AC26" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="AD26" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE26" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AF26" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="AG26" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AH26" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AI26" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AJ26" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AK26" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="AL26" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="AM26" s="24">
+        <f t="array" ref="AM26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>44</v>
+      </c>
+      <c r="AN26" s="24" t="str">
+        <f t="array" ref="AN26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>変態植物倶楽部の店</v>
+      </c>
+      <c r="AO26" s="25" t="str">
+        <f t="array" ref="AO26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/pureko.yakisoba___</v>
+      </c>
+      <c r="AP26" s="24" t="str">
+        <f t="array" ref="AP26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区泉尾１丁目２２−１２</v>
+      </c>
+      <c r="AQ26" s="25" t="str">
+        <f t="array" ref="AQ26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/7LxwLtzxhZXxzxw59</v>
       </c>
     </row>
   </sheetData>
@@ -3919,10 +4456,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -3930,19 +4467,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -3950,19 +4487,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -3970,19 +4507,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -3990,19 +4527,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -4010,19 +4547,19 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -4030,19 +4567,19 @@
         <v>34.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>101</v>
+        <v>86</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -4050,19 +4587,19 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4070,19 +4607,19 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -4090,19 +4627,19 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -4119,10 +4656,10 @@
         <v>123</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -4130,19 +4667,19 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>130</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="16">
@@ -4150,19 +4687,19 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
@@ -4170,19 +4707,19 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
@@ -4190,19 +4727,19 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="19">
@@ -4210,19 +4747,19 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="20">
@@ -4230,19 +4767,19 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21">
@@ -4250,19 +4787,19 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
@@ -4270,19 +4807,19 @@
         <v>29.0</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="23">
@@ -4290,19 +4827,19 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="E23" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="24">
@@ -4310,7 +4847,7 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>187</v>
@@ -4330,19 +4867,19 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26">
@@ -4350,13 +4887,13 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>208</v>
@@ -4377,7 +4914,7 @@
         <v>211</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F27" s="19"/>
     </row>
@@ -4386,19 +4923,19 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
@@ -4406,19 +4943,19 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30">
@@ -4426,19 +4963,19 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31">
@@ -4446,19 +4983,19 @@
         <v>35.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="32">
@@ -4466,19 +5003,19 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33">
@@ -4486,19 +5023,19 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34">
@@ -4525,7 +5062,7 @@
       <c r="A35" s="3">
         <v>32.0</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="20" t="s">
         <v>272</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -4545,7 +5082,7 @@
       <c r="A36" s="3">
         <v>33.0</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="21" t="s">
         <v>277</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -4572,7 +5109,7 @@
         <v>283</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>288</v>
@@ -4601,7 +5138,7 @@
       <c r="A39" s="3">
         <v>38.0</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="20" t="s">
         <v>293</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -4610,7 +5147,7 @@
       <c r="D39" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F39" s="19"/>
@@ -4647,10 +5184,10 @@
         <v>303</v>
       </c>
       <c r="E41" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F41" s="12" t="s">
         <v>305</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="42">
@@ -4658,19 +5195,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F42" s="15" t="s">
-        <v>316</v>
+      <c r="F42" s="12" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="43">
@@ -4689,7 +5226,7 @@
       <c r="E43" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="12" t="s">
         <v>321</v>
       </c>
     </row>
@@ -4709,7 +5246,7 @@
       <c r="E44" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="12" t="s">
         <v>326</v>
       </c>
     </row>
@@ -4718,19 +5255,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>328</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>329</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>330</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="46">
@@ -4747,7 +5284,7 @@
         <v>339</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F46" s="19"/>
     </row>
@@ -4803,7 +5340,7 @@
       <c r="E49" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="12" t="s">
         <v>354</v>
       </c>
     </row>
@@ -4812,19 +5349,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="F50" s="15" t="s">
         <v>361</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="51">
@@ -4832,19 +5369,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>367</v>
+        <v>377</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="52">
@@ -4852,19 +5389,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>372</v>
+        <v>382</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="53">
@@ -4872,19 +5409,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>377</v>
+        <v>387</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="54">
@@ -4892,19 +5429,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>384</v>
+        <v>395</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="55">
@@ -4912,19 +5449,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>398</v>
+        <v>402</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="56">
@@ -4932,17 +5469,17 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C56" s="23"/>
       <c r="D56" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>402</v>
+        <v>406</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="57">
@@ -4950,35 +5487,35 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C57" s="23"/>
       <c r="D57" s="5" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>405</v>
+        <v>406</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
         <v>57.0</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>406</v>
+      <c r="B58" s="20" t="s">
+        <v>412</v>
       </c>
       <c r="C58" s="23"/>
       <c r="D58" s="5" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="F58" s="15" t="s">
         <v>414</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="59">
@@ -4986,17 +5523,17 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C59" s="23"/>
       <c r="D59" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>418</v>
+        <v>420</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="60">
@@ -5004,11 +5541,11 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C60" s="23"/>
       <c r="D60" s="5" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="61">
@@ -5016,11 +5553,11 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="C61" s="23"/>
       <c r="D61" s="5" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
+++ b/data/大正酔いどれクエストⅡ　店舗情報アンケート（回答）.xlsx
@@ -7,7 +7,7 @@
     <sheet state="visible" name="シート1" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'フォームの回答 1'!$A$1:$AQ$26</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'フォームの回答 1'!$A$1:$AQ$27</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="486">
   <si>
     <t>ID</t>
   </si>
@@ -118,51 +118,90 @@
     <t>https://www.instagram.com/haiena_haitu</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家西１丁目５−７</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
+  </si>
+  <si>
+    <t>CHWEETS</t>
+  </si>
+  <si>
+    <t>クレープ酒場・夜カフェ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chweets_1138</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目１７−１７</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
+  </si>
+  <si>
+    <t>BAR K'S〜ケーズ〜</t>
+  </si>
+  <si>
+    <t>ダーツ・カラオケ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_ks_taisho</t>
+  </si>
+  <si>
     <t>タイムスタンプ</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目５−７</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</t>
+    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2D</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
+  </si>
+  <si>
+    <t>Bar Six Nine</t>
+  </si>
+  <si>
+    <t>ショットバー</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_six_nine_0692</t>
   </si>
   <si>
     <t>店名</t>
   </si>
   <si>
-    <t>CHWEETS</t>
-  </si>
-  <si>
-    <t>クレープ酒場・夜カフェ</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/chweets_1138</t>
-  </si>
-  <si>
     <t>大正酔いどれクエストⅡに参加されますか？</t>
   </si>
   <si>
     <t xml:space="preserve">  エリア  </t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目５</t>
+  </si>
+  <si>
     <t>カテゴリ</t>
   </si>
   <si>
+    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
+  </si>
+  <si>
     <t>スタイル</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目１７−１７</t>
-  </si>
-  <si>
     <t>タイプ</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/rBmQt912byGEZgbU7</t>
-  </si>
-  <si>
     <t>テイクアウト</t>
   </si>
   <si>
+    <t>B.B.QホルモンMOU</t>
+  </si>
+  <si>
+    <t>立ち飲み・ホルモン</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bbq.mou.29</t>
+  </si>
+  <si>
     <t>どれクエ対応曜日</t>
   </si>
   <si>
@@ -172,127 +211,19 @@
     <t>どれクエ対応時間：終了</t>
   </si>
   <si>
-    <t>BAR K'S〜ケーズ〜</t>
-  </si>
-  <si>
-    <t>ダーツ・カラオケ</t>
-  </si>
-  <si>
     <t>提供時間に対する補足</t>
   </si>
   <si>
-    <t>https://www.instagram.com/bar_ks_taisho</t>
-  </si>
-  <si>
     <t>決済方法</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目２−４</t>
+  </si>
+  <si>
     <t>店舗クーポンを希望されますか？</t>
   </si>
   <si>
     <t xml:space="preserve">  「どれクエⅡ」にはどの企画で参加されますか？  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  酔いどれセット名  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  酔いどれセット内容  </t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正2D</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/h1iC1PzMoU3TmyDg9</t>
-  </si>
-  <si>
-    <t>セット内容備考</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  価格(税込)  </t>
-  </si>
-  <si>
-    <t>チャージ料(税込)</t>
-  </si>
-  <si>
-    <t>限定数量</t>
-  </si>
-  <si>
-    <t>クエスト名</t>
-  </si>
-  <si>
-    <t>Bar Six Nine</t>
-  </si>
-  <si>
-    <t>ショットバー</t>
-  </si>
-  <si>
-    <t>クエスト内容/報酬</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bar_six_nine_0692</t>
-  </si>
-  <si>
-    <t>クエスト料金(税込)</t>
-  </si>
-  <si>
-    <t>クエストチャージ料 (税込)</t>
-  </si>
-  <si>
-    <t>クエスト備考</t>
-  </si>
-  <si>
-    <t>酔いどれセット名</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  酔いどれセット内容   2</t>
-  </si>
-  <si>
-    <t>セット内容備考 2</t>
-  </si>
-  <si>
-    <t>価格(税込)</t>
-  </si>
-  <si>
-    <t>チャージ料(税込) 2</t>
-  </si>
-  <si>
-    <t>B.B.QホルモンMOU</t>
-  </si>
-  <si>
-    <t>限定数量 2</t>
-  </si>
-  <si>
-    <t>立ち飲み・ホルモン</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/bbq.mou.29</t>
-  </si>
-  <si>
-    <t>クエスト名 2</t>
-  </si>
-  <si>
-    <t>クエスト内容/報酬 2</t>
-  </si>
-  <si>
-    <t>クエスト料金(税込) 2</t>
-  </si>
-  <si>
-    <t>クエストチャージ料 (税込) 2</t>
-  </si>
-  <si>
-    <t>クエスト備考 2</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目２−４</t>
-  </si>
-  <si>
-    <t>お客様向け参加証(缶バッチ)　販売希望数は？</t>
   </si>
   <si>
     <r>
@@ -306,21 +237,150 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">  酔いどれセット名  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  酔いどれセット内容  </t>
+  </si>
+  <si>
+    <t>セット内容備考</t>
+  </si>
+  <si>
     <t>だしと鶏ちゃぼ大正店</t>
   </si>
   <si>
+    <t xml:space="preserve">  価格(税込)  </t>
+  </si>
+  <si>
     <t>焼き鳥・お出汁料理</t>
   </si>
   <si>
     <t>https://www.instagram.com/chabo_taisho</t>
   </si>
   <si>
+    <t>チャージ料(税込)</t>
+  </si>
+  <si>
+    <t>限定数量</t>
+  </si>
+  <si>
+    <t>クエスト名</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家東１丁目１７−１６</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</t>
   </si>
   <si>
+    <t>クエスト内容/報酬</t>
+  </si>
+  <si>
+    <t>クエスト料金(税込)</t>
+  </si>
+  <si>
+    <t>クエストチャージ料 (税込)</t>
+  </si>
+  <si>
+    <t>ふじわら君</t>
+  </si>
+  <si>
+    <t>創作料理居酒屋</t>
+  </si>
+  <si>
+    <t>クエスト備考</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fujiwarakun_taisho</t>
+  </si>
+  <si>
+    <t>酔いどれセット名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  酔いどれセット内容   2</t>
+  </si>
+  <si>
+    <t>セット内容備考 2</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目１−７</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
+  </si>
+  <si>
+    <t>価格(税込)</t>
+  </si>
+  <si>
+    <t>チャージ料(税込) 2</t>
+  </si>
+  <si>
+    <t>限定数量 2</t>
+  </si>
+  <si>
+    <t>大正サロン髭とボヰン</t>
+  </si>
+  <si>
+    <t>立ち飲み・創作料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hige_to.boin</t>
+  </si>
+  <si>
+    <t>クエスト名 2</t>
+  </si>
+  <si>
+    <t>クエスト内容/報酬 2</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目５−１４</t>
+  </si>
+  <si>
+    <t>クエスト料金(税込) 2</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
+  </si>
+  <si>
+    <t>クエストチャージ料 (税込) 2</t>
+  </si>
+  <si>
+    <t>クエスト備考 2</t>
+  </si>
+  <si>
+    <t>大正バル誠~ｓｅｉ~</t>
+  </si>
+  <si>
+    <t>お客様向け参加証(缶バッチ)　販売希望数は？</t>
+  </si>
+  <si>
+    <t>串カツ・牡蠣・沖縄料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_sei</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目３−１１</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
+  </si>
+  <si>
+    <t>居酒屋たすいち</t>
+  </si>
+  <si>
+    <t>もつ鍋酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/izakaya_tasuichi</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目８−２３</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
+  </si>
+  <si>
     <t>参加する</t>
   </si>
   <si>
@@ -330,31 +390,40 @@
     <t>おばんざい</t>
   </si>
   <si>
-    <t>ふじわら君</t>
-  </si>
-  <si>
-    <t>創作料理居酒屋</t>
-  </si>
-  <si>
     <t>テールブあり</t>
   </si>
   <si>
-    <t>https://www.instagram.com/fujiwarakun_taisho</t>
+    <t>地鶏る</t>
+  </si>
+  <si>
+    <t>宮崎鶏の炭火焼き</t>
   </si>
   <si>
     <t>サク飲み</t>
   </si>
   <si>
+    <t>https://www.instagram.com/jidoru_1013</t>
+  </si>
+  <si>
+    <t>大阪市大正区泉尾３丁目２−７ 1階</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
+  </si>
+  <si>
     <t>テイクアウトOK</t>
   </si>
   <si>
     <t>日曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家西１丁目１−７</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</t>
+    <t>沖縄酒場きじむなーの森</t>
+  </si>
+  <si>
+    <t>沖縄料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
   </si>
   <si>
     <t>土日祝は15時～22時</t>
@@ -366,190 +435,217 @@
     <t>はい。希望します。</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家西１丁目１−１４ タグボート大正 2F</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
+  </si>
+  <si>
     <t>「酔いどれセット」のみで参加</t>
   </si>
   <si>
-    <t>大正サロン髭とボヰン</t>
-  </si>
-  <si>
-    <t>立ち飲み・創作料理</t>
-  </si>
-  <si>
     <t>選べるおばんざい3種セット</t>
   </si>
   <si>
-    <t>https://www.instagram.com/hige_to.boin</t>
-  </si>
-  <si>
     <t>おばんざい小盛3種+ドリンク1杯</t>
   </si>
   <si>
+    <t>ナンチャツ亭のエリー</t>
+  </si>
+  <si>
+    <t>昭和レトロなおばんざい</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nanchatteino_erie</t>
+  </si>
+  <si>
     <t>数種類あるおばんざいから3種類選べます。</t>
   </si>
   <si>
-    <t>800円(税込)</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５−１４</t>
-  </si>
-  <si>
     <t>酔いどれセットの方は０円</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/SGWcKvKGnM5jmSea6</t>
+    <t>大阪市大正区三軒家東１丁目１７−３３ 平和相互商事大正橋ビル 1F</t>
   </si>
   <si>
     <t>おばんざいが無くなるまで。</t>
   </si>
   <si>
-    <t>大正バル誠~ｓｅｉ~</t>
-  </si>
-  <si>
-    <t>串カツ・牡蠣・沖縄料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/izakaya_sei</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目３−１１</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/2TSaY99KjvafbH728</t>
-  </si>
-  <si>
-    <t>居酒屋たすいち</t>
-  </si>
-  <si>
-    <t>もつ鍋酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/izakaya_tasuichi</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目８−２３</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/GSNQFGQG6kZgSscz7</t>
-  </si>
-  <si>
-    <t>地鶏る</t>
-  </si>
-  <si>
-    <t>宮崎鶏の炭火焼き</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/jidoru_1013</t>
-  </si>
-  <si>
-    <t>大阪市大正区泉尾３丁目２−７ 1階</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xrZVAtv7kBYFbYxU8</t>
-  </si>
-  <si>
-    <t>沖縄酒場きじむなーの森</t>
-  </si>
-  <si>
-    <t>沖縄料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kijimuna_no_mori.03.03</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目１−１４ タグボート大正 2F</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/BYfv2YxJfrB6RUYV8</t>
+    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
+  </si>
+  <si>
+    <t>Neboke-ネボケ</t>
+  </si>
+  <si>
+    <t>隠れ家バー</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/Neboke_bar</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
+  </si>
+  <si>
+    <t>串焼き酒場ニコヤ</t>
+  </si>
+  <si>
+    <t>創作鉄板串焼き</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicoya1203</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目２５−１０ 1階</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
+  </si>
+  <si>
+    <t>Barカセット</t>
+  </si>
+  <si>
+    <t>80's・ロック・駄菓子</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/showz0069</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目２−５ 1F</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
+  </si>
+  <si>
+    <t>焼肉ホルモンたろちゃん大正橋店</t>
+  </si>
+  <si>
+    <t>駅前で昼から飲める店</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tarochan_taisho</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目２−６</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
+  </si>
+  <si>
+    <t>鉄板焼き栄八大阪大正店</t>
+  </si>
+  <si>
+    <t>お好み・焼きそば・鉄板居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/teppanyaki_eihachi</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目６−３</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
+  </si>
+  <si>
+    <t>うて食堂 大正BASE</t>
+  </si>
+  <si>
+    <t>蒸し料理で飲める食堂</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ura_omote.shokudou</t>
   </si>
   <si>
     <t>駅前</t>
   </si>
   <si>
+    <t>大阪市大正区三軒家東１丁目１０−２１</t>
+  </si>
+  <si>
     <t>ジビエ肉</t>
   </si>
   <si>
+    <t>https://maps.app.goo.gl/rc5NfzqfDAM7pevWA</t>
+  </si>
+  <si>
     <t>テーブルあり</t>
   </si>
   <si>
-    <t>ナンチャツ亭のエリー</t>
-  </si>
-  <si>
     <t>腹ごしらえ</t>
   </si>
   <si>
-    <t>昭和レトロなおばんざい</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nanchatteino_erie</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目１７−３３ 平和相互商事大正橋ビル 1F</t>
+    <t>大正焼肉ホルモンK2+</t>
+  </si>
+  <si>
+    <t>焼肉ホルモン・韓国料理</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakiniku.k2plus</t>
   </si>
   <si>
     <t>週末延長可能性あり</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</t>
-  </si>
-  <si>
     <t>現金, paypay</t>
   </si>
   <si>
     <t>一品とお酒</t>
   </si>
   <si>
-    <t>Neboke-ネボケ</t>
-  </si>
-  <si>
-    <t>隠れ家バー</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/Neboke_bar</t>
-  </si>
-  <si>
     <t>限定30セット / 日</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/WiS8rFbF993DeBHp9</t>
-  </si>
-  <si>
-    <t>串焼き酒場ニコヤ</t>
-  </si>
-  <si>
-    <t>創作鉄板串焼き</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/nicoya1203</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目２５−１０ 1階</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/xUqC8zQH77DDPQ7c9</t>
-  </si>
-  <si>
-    <t>Barカセット</t>
-  </si>
-  <si>
-    <t>80's・ロック・駄菓子</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/showz0069</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目２−５ 1F</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</t>
-  </si>
-  <si>
-    <t>焼肉ホルモンたろちゃん大正橋店</t>
-  </si>
-  <si>
-    <t>駅前で昼から飲める店</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/tarochan_taisho</t>
+    <t>大阪市大正区三軒家西１丁目９−３６</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
+  </si>
+  <si>
+    <t>呑み処 三日月</t>
+  </si>
+  <si>
+    <t>カラオケ居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moon.3.3.3</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目４−８</t>
+  </si>
+  <si>
+    <t>呑笑戎屋</t>
+  </si>
+  <si>
+    <t>地元親子の大衆居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ebisuya.taisyo</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家東１丁目５－１０</t>
+  </si>
+  <si>
+    <t>三ちゃん</t>
+  </si>
+  <si>
+    <t>海鮮居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sanchan.o2</t>
+  </si>
+  <si>
+    <t>大阪市大正区三軒家西１丁目１７−２０</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
+  </si>
+  <si>
+    <t>SoundBar花いち</t>
+  </si>
+  <si>
+    <t>カラオケバー</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/soundbar__hanaichi</t>
   </si>
   <si>
     <t>クレープ</t>
@@ -558,10 +654,10 @@
     <t>ひと休み</t>
   </si>
   <si>
-    <t>大阪市大正区三軒家東１丁目２−６</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/P1ytbeyLANs4TgD19</t>
+    <t>大阪市大正区三軒家東１丁目５−１４ 2階</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
   </si>
   <si>
     <t>火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
@@ -570,7 +666,13 @@
     <t>現金</t>
   </si>
   <si>
-    <t>鉄板焼き栄八大阪大正店</t>
+    <t>ザ·沖縄</t>
+  </si>
+  <si>
+    <t>沖縄料理・カラオケ居酒屋</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/za.okinawa</t>
   </si>
   <si>
     <t>ピロークレープとハンドドリップコーヒー</t>
@@ -579,174 +681,9 @@
     <t>包みタイプのクレープとハンドドリップコーヒーのセットです</t>
   </si>
   <si>
-    <t>お好み・焼きそば・鉄板居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/teppanyaki_eihachi</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目６−３</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</t>
-  </si>
-  <si>
-    <t>クラスノ</t>
-  </si>
-  <si>
-    <t>うて食堂 大正BASE</t>
-  </si>
-  <si>
-    <t>参加しない</t>
-  </si>
-  <si>
-    <t>蒸し料理で飲める食堂</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/ura_omote.shokudou</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目１０−２１</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/rc5NfzqfDAM7pevWA</t>
-  </si>
-  <si>
-    <t>ナンチャッ亭のエリー</t>
-  </si>
-  <si>
-    <t>三軒家東</t>
-  </si>
-  <si>
-    <t>カウンター</t>
-  </si>
-  <si>
-    <t>テイクアウト不可</t>
-  </si>
-  <si>
-    <t>日曜日, 月曜日, 木曜日, 金曜日, 土曜日</t>
-  </si>
-  <si>
-    <t>大正焼肉ホルモンK2+</t>
-  </si>
-  <si>
-    <t>焼肉ホルモン・韓国料理</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/yakiniku.k2plus</t>
-  </si>
-  <si>
-    <t>一休みセット</t>
-  </si>
-  <si>
-    <t>ひと口おばんざいセットと1ドリンク</t>
-  </si>
-  <si>
-    <t>お腹に優しいおばんざいひと口サイズの盛り合わせ</t>
-  </si>
-  <si>
-    <t>限定30</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目９−３６</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/9Wt44gRpXPDoTt1q9</t>
-  </si>
-  <si>
-    <t>呑み処 三日月</t>
-  </si>
-  <si>
-    <t>カラオケ居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/moon.3.3.3</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目４−８</t>
-  </si>
-  <si>
-    <t>呑笑戎屋</t>
-  </si>
-  <si>
-    <t>地元親子の大衆居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/ebisuya.taisyo</t>
-  </si>
-  <si>
-    <t>バーガー酒場「ハンバーガー・ママ」</t>
-  </si>
-  <si>
-    <t>ハンバーガー</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５－１０</t>
-  </si>
-  <si>
-    <t>三ちゃん</t>
-  </si>
-  <si>
-    <t>海鮮居酒屋</t>
-  </si>
-  <si>
-    <t>月曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/sanchan.o2</t>
-  </si>
-  <si>
-    <t>火・木は18:00オープン</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード, 各種QR決済</t>
-  </si>
-  <si>
-    <t>どれクエII限定ミニバーガー＋ドリンクセット</t>
-  </si>
-  <si>
-    <t>イベント期間限定ミニバーガー＋ちょいポテト＋1ドリンク</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家西１丁目１７−２０</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/DXhUb1vmR7aNUMMT8</t>
-  </si>
-  <si>
-    <t>1,000円</t>
-  </si>
-  <si>
-    <t>SoundBar花いち</t>
-  </si>
-  <si>
-    <t>カラオケバー</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/soundbar__hanaichi</t>
-  </si>
-  <si>
-    <t>大阪市大正区三軒家東１丁目５−１４ 2階</t>
-  </si>
-  <si>
-    <t>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</t>
-  </si>
-  <si>
-    <t>ザ·沖縄</t>
-  </si>
-  <si>
-    <t>沖縄料理・カラオケ居酒屋</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/za.okinawa</t>
-  </si>
-  <si>
     <t>https://maps.app.goo.gl/Prnu5oBX6hyQzpft6</t>
   </si>
   <si>
-    <t>BARカセット</t>
-  </si>
-  <si>
     <t>NONA</t>
   </si>
   <si>
@@ -754,12 +691,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/cafe.bar.nona9</t>
-  </si>
-  <si>
-    <t>BAR</t>
-  </si>
-  <si>
-    <t>夜遊び</t>
   </si>
   <si>
     <t>大阪市大正区泉尾２丁目１１−９</t>
@@ -776,12 +707,6 @@
     </r>
   </si>
   <si>
-    <t>全て</t>
-  </si>
-  <si>
-    <t>店舗STAFFのシフトにより若干の時間変動あり</t>
-  </si>
-  <si>
     <t>魚と沖縄料理 えっせんす</t>
   </si>
   <si>
@@ -791,33 +716,12 @@
     <t>https://www.instagram.com/essence_taishou</t>
   </si>
   <si>
-    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
-  </si>
-  <si>
-    <t>ぐんたいガニ捕獲セット（カニぱん）</t>
-  </si>
-  <si>
-    <t>ドリンクを注文したお客様に三立製菓さんの「かにパン」をプレゼント！</t>
-  </si>
-  <si>
     <t>大阪市大正区泉尾３丁目１２−１７ 泉尾商店 街内</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/NL1uEH8kq3MhMEzdA</t>
   </si>
   <si>
-    <t>店頭で捕獲したぐんたいガ二（かにパン）は、その場で食べても良し！持ち帰って、明日のパンにしても良し！</t>
-  </si>
-  <si>
-    <t>1000円</t>
-  </si>
-  <si>
-    <t>500円</t>
-  </si>
-  <si>
-    <t>30セット予定（好評の場合追加有り）</t>
-  </si>
-  <si>
     <t>Bar Coco-Color</t>
   </si>
   <si>
@@ -827,27 +731,12 @@
     <t>https://www.instagram.com/bar_cococolor_taisho</t>
   </si>
   <si>
-    <t>ぐんたいガニ乱獲クエスト</t>
-  </si>
-  <si>
-    <t>追加ドリンクを注文して頂いたお客様に「勇者のサイコロ」でSTAFFに挑戦して貰います。見事STAFFに勝利したお客様には三立製菓さんの「かにビス」をプレゼント！</t>
-  </si>
-  <si>
-    <t>追加ドリンクの料金500円～900円（スコッチは除く）</t>
-  </si>
-  <si>
-    <t>追加ドリンクの料金のみ</t>
-  </si>
-  <si>
     <t>大阪市大正区三軒家西１丁目１６−１６</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</t>
   </si>
   <si>
-    <t>2酔いどれセットご注文、又は2杯目以降のご注文から挑戦して頂けます</t>
-  </si>
-  <si>
     <t>福人(ふくんちゅ)</t>
   </si>
   <si>
@@ -857,6 +746,12 @@
     <t>https://www.instagram.com/fuku__nchu</t>
   </si>
   <si>
+    <t>クラスノ</t>
+  </si>
+  <si>
+    <t>参加しない</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家東１丁目１６−２６</t>
   </si>
   <si>
@@ -902,27 +797,27 @@
     <t>https://www.instagram.com/okonomiyaki_mamama15</t>
   </si>
   <si>
-    <t>いいえ、希望しません。</t>
-  </si>
-  <si>
-    <t>1000円セット</t>
-  </si>
-  <si>
-    <t>ドリンク1杯+おつまみ</t>
-  </si>
-  <si>
     <t>大阪市大正区三軒家東１丁目１７−３３ 2F</t>
   </si>
   <si>
     <t>スナック チェリー</t>
   </si>
   <si>
+    <t>ナンチャッ亭のエリー</t>
+  </si>
+  <si>
     <t>ゴルフ好き集まれ</t>
   </si>
   <si>
     <t>https://www.instagram.com/cherry.taisho</t>
   </si>
   <si>
+    <t>三軒家東</t>
+  </si>
+  <si>
+    <t>カウンター</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家東１丁目１６ー１６ 2階</t>
   </si>
   <si>
@@ -935,6 +830,12 @@
     <t>https://www.instagram.com/__2knme0703</t>
   </si>
   <si>
+    <t>テイクアウト不可</t>
+  </si>
+  <si>
+    <t>日曜日, 月曜日, 木曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家西１丁目４−１６ベルコモンズ大正</t>
   </si>
   <si>
@@ -947,9 +848,18 @@
     <t>https://www.instagram.com/fine.r11123</t>
   </si>
   <si>
+    <t>一休みセット</t>
+  </si>
+  <si>
+    <t>ひと口おばんざいセットと1ドリンク</t>
+  </si>
+  <si>
     <t>大阪市大正区三軒家東1-2-6 サンコークリスタル701</t>
   </si>
   <si>
+    <t>お腹に優しいおばんざいひと口サイズの盛り合わせ</t>
+  </si>
+  <si>
     <t>BAR EDIT</t>
   </si>
   <si>
@@ -957,6 +867,9 @@
   </si>
   <si>
     <t>https://www.instagram.com/bar_edit_osaka</t>
+  </si>
+  <si>
+    <t>限定30</t>
   </si>
   <si>
     <t>大阪市大正区泉尾１丁目３０−１５ 平本ビル</t>
@@ -973,9 +886,6 @@
     </r>
   </si>
   <si>
-    <t>その日の状況により早く閉める場合あり。</t>
-  </si>
-  <si>
     <t>うおしんのご愛嬌</t>
   </si>
   <si>
@@ -983,18 +893,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/uoshin_no_goaikyou</t>
-  </si>
-  <si>
-    <t>花いちオリジナルセット</t>
-  </si>
-  <si>
-    <t>700円までのドリンク1杯+チャーム+カラオケ無料</t>
-  </si>
-  <si>
-    <t>特になし</t>
-  </si>
-  <si>
-    <t>なし</t>
   </si>
   <si>
     <r>
@@ -1008,12 +906,6 @@
     </r>
   </si>
   <si>
-    <t>カラオケで95点以上にチャレンジ！！</t>
-  </si>
-  <si>
-    <t>カラオケで95点以上出した方に、〆のカップ麺1個プレゼント！！</t>
-  </si>
-  <si>
     <t>9回の表</t>
   </si>
   <si>
@@ -1060,22 +952,22 @@
     </r>
   </si>
   <si>
+    <t>バーガー酒場「ハンバーガー・ママ」</t>
+  </si>
+  <si>
     <t>鉄板焼き ぷれこ</t>
   </si>
   <si>
     <t>変態植物倶楽部の店</t>
   </si>
   <si>
-    <t>居酒屋</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/pureko.yakisoba___</t>
   </si>
   <si>
+    <t>ハンバーガー</t>
+  </si>
+  <si>
     <t>大阪市大正区泉尾１丁目２２−１２</t>
-  </si>
-  <si>
-    <t>22時以降も席とお店が開いていればOK</t>
   </si>
   <si>
     <r>
@@ -1089,13 +981,7 @@
     </r>
   </si>
   <si>
-    <t>現金, paypay, クレジットカード</t>
-  </si>
-  <si>
-    <t>誠seiセット</t>
-  </si>
-  <si>
-    <t>ワンドリンク＋串カツ５本or牡蠣セット</t>
+    <t>月曜日, 火曜日, 水曜日, 木曜日, 金曜日, 土曜日</t>
   </si>
   <si>
     <t>かのじょとカレー</t>
@@ -1107,12 +993,24 @@
     <t>https://www.instagram.com/sheandcurry</t>
   </si>
   <si>
+    <t>火・木は18:00オープン</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, 各種QR決済</t>
+  </si>
+  <si>
+    <t>どれクエII限定ミニバーガー＋ドリンクセット</t>
+  </si>
+  <si>
     <t>呑め屋 集合！</t>
   </si>
   <si>
     <t>素朴な家庭料理</t>
   </si>
   <si>
+    <t>イベント期間限定ミニバーガー＋ちょいポテト＋1ドリンク</t>
+  </si>
+  <si>
     <t>https://www.instagram.com/syuugo_ma_0418</t>
   </si>
   <si>
@@ -1138,12 +1036,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/horumonyaki_miyake</t>
-  </si>
-  <si>
-    <t>中華メインの居酒屋</t>
-  </si>
-  <si>
-    <t>1F立ち飲み2Fテーブル</t>
   </si>
   <si>
     <t>大阪市大正区三軒家東１丁目１０−２２ 1階</t>
@@ -1160,15 +1052,6 @@
     </r>
   </si>
   <si>
-    <t>元気玉セット</t>
-  </si>
-  <si>
-    <t>元気玉+黒糖焼酎（じょうご）一杯</t>
-  </si>
-  <si>
-    <t>未定</t>
-  </si>
-  <si>
     <t>酒と魚 喰海~KUKAI~</t>
   </si>
   <si>
@@ -1192,22 +1075,7 @@
     </r>
   </si>
   <si>
-    <t>焼肉・ホルモン</t>
-  </si>
-  <si>
-    <t>現金, paypay, クレジットカード, 電子マネー</t>
-  </si>
-  <si>
-    <t>選べる名物厚切り肉！</t>
-  </si>
-  <si>
-    <t>好きなドリンク1杯と名物の厚切り上塩タンか厚切り特上ハラミどちらかを選んでもらえるセット</t>
-  </si>
-  <si>
-    <t>酔いどれセットのテイクアウト不可</t>
-  </si>
-  <si>
-    <t>2,000円</t>
+    <t>BARカセット</t>
   </si>
   <si>
     <t>Zakky's ホットドッグ</t>
@@ -1216,25 +1084,16 @@
     <t>大正アメリンカンダイナー</t>
   </si>
   <si>
-    <t>0円</t>
-  </si>
-  <si>
     <t>https://www.instagram.com/zakkys_hotdog</t>
   </si>
   <si>
-    <t>期間中いつでも可</t>
-  </si>
-  <si>
-    <t>ピンゾロチャレンジ</t>
-  </si>
-  <si>
-    <t>サイコロで1のゾロ目が出たら酔いどれセットが半額になる</t>
-  </si>
-  <si>
-    <t>10個</t>
+    <t>BAR</t>
   </si>
   <si>
     <t>大阪市大正区千島３丁目１２−１３ ハイグレード千島</t>
+  </si>
+  <si>
+    <t>夜遊び</t>
   </si>
   <si>
     <r>
@@ -1248,6 +1107,9 @@
     </r>
   </si>
   <si>
+    <t>全て</t>
+  </si>
+  <si>
     <t>立ち飲み居酒屋まるとく大正店</t>
   </si>
   <si>
@@ -1255,6 +1117,9 @@
   </si>
   <si>
     <t>https://www.instagram.com/mrtk.taishou</t>
+  </si>
+  <si>
+    <t>店舗STAFFのシフトにより若干の時間変動あり</t>
   </si>
   <si>
     <t>大阪市大正区三軒家西1-4-15大正コペンシル1階</t>
@@ -1271,6 +1136,15 @@
     </r>
   </si>
   <si>
+    <t>「酔いどれセット」・「店舗クエスト」両方で参加</t>
+  </si>
+  <si>
+    <t>ぐんたいガニ捕獲セット（カニぱん）</t>
+  </si>
+  <si>
+    <t>ドリンクを注文したお客様に三立製菓さんの「かにパン」をプレゼント！</t>
+  </si>
+  <si>
     <t>呑めるおばんざい処 和んでや</t>
   </si>
   <si>
@@ -1278,6 +1152,12 @@
   </si>
   <si>
     <t>https://www.instagram.com/nagondeyaaa</t>
+  </si>
+  <si>
+    <t>店頭で捕獲したぐんたいガ二（かにパン）は、その場で食べても良し！持ち帰って、明日のパンにしても良し！</t>
+  </si>
+  <si>
+    <t>30セット予定（好評の場合追加有り）</t>
   </si>
   <si>
     <t>大阪市大正区三軒家東１丁目２１−１５</t>
@@ -1294,6 +1174,18 @@
     </r>
   </si>
   <si>
+    <t>ぐんたいガニ乱獲クエスト</t>
+  </si>
+  <si>
+    <t>追加ドリンクを注文して頂いたお客様に「勇者のサイコロ」でSTAFFに挑戦して貰います。見事STAFFに勝利したお客様には三立製菓さんの「かにビス」をプレゼント！</t>
+  </si>
+  <si>
+    <t>500～900</t>
+  </si>
+  <si>
+    <t>追加ドリンクの料金のみ</t>
+  </si>
+  <si>
     <t>3PIECE</t>
   </si>
   <si>
@@ -1303,13 +1195,7 @@
     <t>https://www.instagram.com/3piece_osake</t>
   </si>
   <si>
-    <t>3:30飲み放題ラストオーダー、4:30で終了、退店</t>
-  </si>
-  <si>
-    <t>現金, クレジットカード, Paypay、D払い以外のバーコード決済</t>
-  </si>
-  <si>
-    <t>1H飲み放題1000円</t>
+    <t>スコッチ以外のドリンクで、酔いどれセットご注文、又は2杯目以降のご注文から挑戦して頂けます</t>
   </si>
   <si>
     <t>大阪市大正区南恩加島６丁目７−８</t>
@@ -1326,12 +1212,6 @@
     </r>
   </si>
   <si>
-    <t>1H飲み放題1000円(チャージ料込み)</t>
-  </si>
-  <si>
-    <t>ラストオーダー15分前、入店3:30まで</t>
-  </si>
-  <si>
     <t>たこ焼き･お好み焼き そーすや</t>
   </si>
   <si>
@@ -1392,13 +1272,19 @@
     </r>
   </si>
   <si>
-    <t>泉尾</t>
-  </si>
-  <si>
     <t>いっぱい呑み 花</t>
   </si>
   <si>
     <t>https://www.instagram.com/ippainomi.hana0806</t>
+  </si>
+  <si>
+    <t>いいえ、希望しません。</t>
+  </si>
+  <si>
+    <t>1000円セット</t>
+  </si>
+  <si>
+    <t>ドリンク1杯+おつまみ</t>
   </si>
   <si>
     <t>大阪市大正区千島3丁目4-7</t>
@@ -1421,16 +1307,7 @@
     <t>https://www.instagram.com/tanom_cafe</t>
   </si>
   <si>
-    <t>ドラクエ限定　一杯目100円</t>
-  </si>
-  <si>
-    <t>入店1杯目100円</t>
-  </si>
-  <si>
     <t>大阪市大正区泉尾１丁目１３−１５</t>
-  </si>
-  <si>
-    <t>無し</t>
   </si>
   <si>
     <r>
@@ -1444,15 +1321,126 @@
     </r>
   </si>
   <si>
+    <t>焼く鳥屋 おかもと 大正店</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakutori_taisho</t>
+  </si>
+  <si>
+    <t>立ち飲み処 雄</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/you_taisho</t>
+  </si>
+  <si>
+    <t>その日の状況により早く閉める場合あり。</t>
+  </si>
+  <si>
+    <t>花いちオリジナルセット</t>
+  </si>
+  <si>
+    <t>700円までのドリンク1杯+チャーム+カラオケ無料</t>
+  </si>
+  <si>
+    <t>特になし</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>カラオケで95点以上にチャレンジ！！</t>
+  </si>
+  <si>
+    <t>カラオケで95点以上出した方に、〆のカップ麺1個プレゼント！！</t>
+  </si>
+  <si>
+    <t>居酒屋</t>
+  </si>
+  <si>
+    <t>22時以降も席とお店が開いていればOK</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード</t>
+  </si>
+  <si>
+    <t>誠seiセット</t>
+  </si>
+  <si>
+    <t>ワンドリンク＋串カツ５本or牡蠣セット</t>
+  </si>
+  <si>
+    <t>中華メインの居酒屋</t>
+  </si>
+  <si>
+    <t>1F立ち飲み2Fテーブル</t>
+  </si>
+  <si>
+    <t>元気玉セット</t>
+  </si>
+  <si>
+    <t>元気玉+黒糖焼酎（じょうご）一杯</t>
+  </si>
+  <si>
+    <t>未定</t>
+  </si>
+  <si>
+    <t>焼肉・ホルモン</t>
+  </si>
+  <si>
+    <t>現金, paypay, クレジットカード, 電子マネー</t>
+  </si>
+  <si>
+    <t>選べる名物厚切り肉！</t>
+  </si>
+  <si>
+    <t>好きなドリンク1杯と名物の厚切り上塩タンか厚切り特上ハラミどちらかを選んでもらえるセット</t>
+  </si>
+  <si>
+    <t>酔いどれセットのテイクアウト不可</t>
+  </si>
+  <si>
+    <t>期間中いつでも可</t>
+  </si>
+  <si>
+    <t>ピンゾロチャレンジ</t>
+  </si>
+  <si>
+    <t>サイコロで1のゾロ目が出たら酔いどれセットが半額になる</t>
+  </si>
+  <si>
+    <t>3:30飲み放題ラストオーダー、4:30で終了、退店</t>
+  </si>
+  <si>
+    <t>現金, クレジットカード, Paypay、D払い以外のバーコード決済</t>
+  </si>
+  <si>
+    <t>1H飲み放題1000円</t>
+  </si>
+  <si>
+    <t>1H飲み放題1000円(チャージ料込み)</t>
+  </si>
+  <si>
+    <t>ラストオーダー15分前、入店3:30まで</t>
+  </si>
+  <si>
+    <t>泉尾</t>
+  </si>
+  <si>
+    <t>ドラクエ限定　一杯目100円</t>
+  </si>
+  <si>
+    <t>入店1杯目100円</t>
+  </si>
+  <si>
+    <t>無し</t>
+  </si>
+  <si>
     <t>立体四目並べ　勝てば、1杯無料</t>
   </si>
   <si>
     <t>勝てば1杯無料</t>
   </si>
   <si>
-    <t>100円</t>
-  </si>
-  <si>
     <t>スパイスカレー</t>
   </si>
   <si>
@@ -1465,45 +1453,24 @@
     <t>15時ラストオーダー　15時30分クローズ</t>
   </si>
   <si>
-    <t>焼く鳥屋 おかもと 大正店</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/yakutori_taisho</t>
-  </si>
-  <si>
     <t>酔いどれカレー</t>
   </si>
   <si>
     <t xml:space="preserve">チキンスパイスカレー小 </t>
   </si>
   <si>
-    <t>800円</t>
-  </si>
-  <si>
     <t>カレーがなくなり次第終了</t>
   </si>
   <si>
     <t>激辛スパイスカレー 4辛</t>
   </si>
   <si>
-    <t>立ち飲み処 雄</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/you_taisho</t>
-  </si>
-  <si>
     <t>4辛のスパイスカレー食べ切ったら、次回スパイスカレー400円引き</t>
   </si>
   <si>
-    <t>1,250円</t>
-  </si>
-  <si>
     <t>激辛です。お子様のチャレンジは出来ません。</t>
   </si>
   <si>
-    <t>5個</t>
-  </si>
-  <si>
     <t>B.B.QホルモンＭＯＵ</t>
   </si>
   <si>
@@ -1519,9 +1486,6 @@
     <t>ホルモンとドリンク</t>
   </si>
   <si>
-    <t>７００</t>
-  </si>
-  <si>
     <t>日曜日, 月曜日, 金曜日, 土曜日</t>
   </si>
   <si>
@@ -1631,9 +1595,6 @@
   </si>
   <si>
     <t>ドリンクは瓶ビール、日本酒を除く</t>
-  </si>
-  <si>
-    <t>1100円(税込)</t>
   </si>
   <si>
     <t>鉄板焼・焼きそば</t>
@@ -1649,6 +1610,9 @@
 </t>
   </si>
   <si>
+    <t>1000円</t>
+  </si>
+  <si>
     <t>限定なし</t>
   </si>
   <si>
@@ -1656,6 +1620,18 @@
   </si>
   <si>
     <t>おまかせします</t>
+  </si>
+  <si>
+    <t>日曜日, 月曜日, 火曜日, 水曜日, 金曜日, 土曜日</t>
+  </si>
+  <si>
+    <t>01:30ラストオーダー</t>
+  </si>
+  <si>
+    <t>お酒orソフトドリンク＋チャーム</t>
+  </si>
+  <si>
+    <t>こちらでよいどれクエスト用のメニューを作って選んでもらいます。</t>
   </si>
 </sst>
 </file>
@@ -1706,14 +1682,14 @@
       <name val="&quot;Meiryo UI&quot;"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="&quot;Meiryo UI&quot;"/>
+    </font>
+    <font>
       <u/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="&quot;Meiryo UI&quot;"/>
     </font>
     <font>
       <u/>
@@ -1755,7 +1731,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1783,6 +1759,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1791,9 +1770,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1807,11 +1783,11 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -1821,6 +1797,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
@@ -1917,8 +1896,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AQ26" displayName="Form_Responses" name="Form_Responses" id="1">
-  <autoFilter ref="$A$1:$AQ$26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AQ27" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$AQ$27"/>
   <tableColumns count="43">
     <tableColumn name="タイムスタンプ" id="1"/>
     <tableColumn name="店名" id="2"/>
@@ -2183,132 +2162,132 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AC1" s="8" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="AD1" s="8" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AE1" s="8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF1" s="8" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="AG1" s="8" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="AH1" s="8" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="AI1" s="8" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="AJ1" s="8" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="AK1" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AL1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="AN1" s="11" t="s">
+      <c r="AN1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AO1" s="11" t="s">
+      <c r="AO1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AP1" s="11" t="s">
+      <c r="AP1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AQ1" s="11" t="s">
+      <c r="AQ1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2320,25 +2299,25 @@
         <v>6</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="J2" s="15">
         <v>0.7083333333357587</v>
@@ -2347,34 +2326,34 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>116</v>
+        <v>140</v>
+      </c>
+      <c r="S2" s="14">
+        <v>800.0</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="AM2" s="16">
         <f t="array" ref="AM2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -2384,7 +2363,7 @@
         <f t="array" ref="AN2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>牛すじとお酒とおばんざい</v>
       </c>
-      <c r="AO2" s="17" t="str">
+      <c r="AO2" s="18" t="str">
         <f t="array" ref="AO2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/t_youbi_</v>
       </c>
@@ -2392,7 +2371,7 @@
         <f t="array" ref="AP2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目４−１５ 大正コペンシルビル 2F</v>
       </c>
-      <c r="AQ2" s="17" t="str">
+      <c r="AQ2" s="18" t="str">
         <f t="array" ref="AQ2">_xlfn.XLOOKUP($B2,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/zEmF7y9d2rdJpG8a7</v>
       </c>
@@ -2405,25 +2384,25 @@
         <v>26</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="J3" s="15">
         <v>0.20833333333575865</v>
@@ -2432,22 +2411,22 @@
         <v>0.45833333333575865</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="N3" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="S3" s="14">
         <v>1000.0</v>
@@ -2456,7 +2435,7 @@
         <v>0.0</v>
       </c>
       <c r="U3" s="14" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AL3" s="14">
         <v>30.0</v>
@@ -2469,7 +2448,7 @@
         <f t="array" ref="AN3">_xlfn.XLOOKUP($B3,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>ジビエ・肉料理</v>
       </c>
-      <c r="AO3" s="17" t="str">
+      <c r="AO3" s="18" t="str">
         <f t="array" ref="AO3">_xlfn.XLOOKUP($B3,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/haiena_haitu</v>
       </c>
@@ -2477,7 +2456,7 @@
         <f t="array" ref="AP3">_xlfn.XLOOKUP($B3,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目５−７</v>
       </c>
-      <c r="AQ3" s="17" t="str">
+      <c r="AQ3" s="18" t="str">
         <f t="array" ref="AQ3">_xlfn.XLOOKUP($B3,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/JVXGfL5NwG4vKz2t6</v>
       </c>
@@ -2487,28 +2466,28 @@
         <v>46292.641919664355</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="J4" s="15">
         <v>0.7916666666642413</v>
@@ -2517,19 +2496,19 @@
         <v>0.9375</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N4" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="S4" s="14">
         <v>1000.0</v>
@@ -2548,7 +2527,7 @@
         <f t="array" ref="AN4">_xlfn.XLOOKUP($B4,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>クレープ酒場・夜カフェ</v>
       </c>
-      <c r="AO4" s="17" t="str">
+      <c r="AO4" s="18" t="str">
         <f t="array" ref="AO4">_xlfn.XLOOKUP($B4,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/chweets_1138</v>
       </c>
@@ -2556,7 +2535,7 @@
         <f t="array" ref="AP4">_xlfn.XLOOKUP($B4,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目１７−１７</v>
       </c>
-      <c r="AQ4" s="17" t="str">
+      <c r="AQ4" s="18" t="str">
         <f t="array" ref="AQ4">_xlfn.XLOOKUP($B4,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/rBmQt912byGEZgbU7</v>
       </c>
@@ -2566,10 +2545,10 @@
         <v>46295.48182782407</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="AM5" s="16" t="str">
         <f t="array" ref="AM5">_xlfn.XLOOKUP($B5,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -2597,28 +2576,28 @@
         <v>46295.488864942134</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="J6" s="15">
         <v>0.7291666666642413</v>
@@ -2627,22 +2606,22 @@
         <v>0.9583333333357587</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="R6" s="14" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="S6" s="14">
         <v>800.0</v>
@@ -2651,7 +2630,7 @@
         <v>0.0</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="AL6" s="14">
         <v>30.0</v>
@@ -2664,7 +2643,7 @@
         <f t="array" ref="AN6">_xlfn.XLOOKUP($B6,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>昭和レトロなおばんざい</v>
       </c>
-      <c r="AO6" s="17" t="str">
+      <c r="AO6" s="18" t="str">
         <f t="array" ref="AO6">_xlfn.XLOOKUP($B6,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/nanchatteino_erie</v>
       </c>
@@ -2672,7 +2651,7 @@
         <f t="array" ref="AP6">_xlfn.XLOOKUP($B6,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目１７−３３ 平和相互商事大正橋ビル 1F</v>
       </c>
-      <c r="AQ6" s="17" t="str">
+      <c r="AQ6" s="18" t="str">
         <f t="array" ref="AQ6">_xlfn.XLOOKUP($B6,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/kGdEWrLq5bwaRyeX7</v>
       </c>
@@ -2682,28 +2661,28 @@
         <v>46295.56995630787</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>212</v>
+        <v>291</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="J7" s="15">
         <v>0.5</v>
@@ -2712,25 +2691,25 @@
         <v>0.0</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>219</v>
+        <v>302</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>220</v>
+        <v>303</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>225</v>
+        <v>307</v>
+      </c>
+      <c r="S7" s="22">
+        <v>1000.0</v>
       </c>
       <c r="T7" s="14">
         <v>0.0</v>
@@ -2764,28 +2743,28 @@
         <v>46295.62130144676</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J8" s="15">
         <v>0.875</v>
@@ -2794,49 +2773,49 @@
         <v>0.125</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA8" s="14" t="s">
-        <v>249</v>
+        <v>340</v>
       </c>
       <c r="AB8" s="14" t="s">
-        <v>250</v>
+        <v>341</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="AD8" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE8" s="14" t="s">
-        <v>255</v>
+        <v>345</v>
+      </c>
+      <c r="AD8" s="14">
+        <v>1000.0</v>
+      </c>
+      <c r="AE8" s="14">
+        <v>500.0</v>
       </c>
       <c r="AF8" s="14" t="s">
-        <v>256</v>
+        <v>346</v>
       </c>
       <c r="AG8" s="14" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="AH8" s="14" t="s">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="AI8" s="14" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="AJ8" s="14" t="s">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="AK8" s="14" t="s">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="AL8" s="14">
         <v>15.0</v>
@@ -2849,7 +2828,7 @@
         <f t="array" ref="AN8">_xlfn.XLOOKUP($B8,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>80's・ロック・駄菓子</v>
       </c>
-      <c r="AO8" s="17" t="str">
+      <c r="AO8" s="18" t="str">
         <f t="array" ref="AO8">_xlfn.XLOOKUP($B8,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/showz0069</v>
       </c>
@@ -2857,7 +2836,7 @@
         <f t="array" ref="AP8">_xlfn.XLOOKUP($B8,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目２−５ 1F</v>
       </c>
-      <c r="AQ8" s="17" t="str">
+      <c r="AQ8" s="18" t="str">
         <f t="array" ref="AQ8">_xlfn.XLOOKUP($B8,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/uUPFxJA4w57PqYzf7</v>
       </c>
@@ -2867,28 +2846,28 @@
         <v>46295.810687523146</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J9" s="15">
         <v>0.8333333333357587</v>
@@ -2897,19 +2876,19 @@
         <v>0.125</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>287</v>
+        <v>375</v>
       </c>
       <c r="S9" s="14">
         <v>1000.0</v>
@@ -2925,7 +2904,7 @@
         <f t="array" ref="AN9">_xlfn.XLOOKUP($B9,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>ショットバー</v>
       </c>
-      <c r="AO9" s="17" t="str">
+      <c r="AO9" s="18" t="str">
         <f t="array" ref="AO9">_xlfn.XLOOKUP($B9,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/bar_six_nine_0692</v>
       </c>
@@ -2933,7 +2912,7 @@
         <f t="array" ref="AP9">_xlfn.XLOOKUP($B9,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目５</v>
       </c>
-      <c r="AQ9" s="17" t="str">
+      <c r="AQ9" s="18" t="str">
         <f t="array" ref="AQ9">_xlfn.XLOOKUP($B9,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/j4hhdwnWPQZ365rk7</v>
       </c>
@@ -2943,28 +2922,28 @@
         <v>46295.91687133102</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J10" s="15">
         <v>0.875</v>
@@ -2973,46 +2952,46 @@
         <v>0.08333333333575865</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>306</v>
+        <v>386</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA10" s="14" t="s">
-        <v>310</v>
+        <v>387</v>
       </c>
       <c r="AB10" s="14" t="s">
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="AC10" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="AD10" s="14" t="s">
-        <v>254</v>
+        <v>389</v>
+      </c>
+      <c r="AD10" s="14">
+        <v>1000.0</v>
       </c>
       <c r="AE10" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="AF10" s="14" t="s">
-        <v>312</v>
+        <v>389</v>
       </c>
       <c r="AG10" s="14" t="s">
-        <v>315</v>
+        <v>391</v>
       </c>
       <c r="AH10" s="14" t="s">
-        <v>316</v>
+        <v>392</v>
       </c>
       <c r="AI10" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="AJ10" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="AL10" s="14">
         <v>5.0</v>
@@ -3025,7 +3004,7 @@
         <f t="array" ref="AN10">_xlfn.XLOOKUP($B10,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>カラオケバー</v>
       </c>
-      <c r="AO10" s="17" t="str">
+      <c r="AO10" s="18" t="str">
         <f t="array" ref="AO10">_xlfn.XLOOKUP($B10,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/soundbar__hanaichi</v>
       </c>
@@ -3033,7 +3012,7 @@
         <f t="array" ref="AP10">_xlfn.XLOOKUP($B10,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目５−１４ 2階</v>
       </c>
-      <c r="AQ10" s="17" t="str">
+      <c r="AQ10" s="18" t="str">
         <f t="array" ref="AQ10">_xlfn.XLOOKUP($B10,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/typkWCnoPJKCUWyH8</v>
       </c>
@@ -3043,28 +3022,28 @@
         <v>46296.49762741898</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J11" s="15">
         <v>0.75</v>
@@ -3073,22 +3052,22 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>332</v>
+        <v>394</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>336</v>
+        <v>397</v>
       </c>
       <c r="S11" s="14">
         <v>1000.0</v>
@@ -3104,7 +3083,7 @@
         <f t="array" ref="AN11">_xlfn.XLOOKUP($B11,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>串カツ・牡蠣・沖縄料理</v>
       </c>
-      <c r="AO11" s="17" t="str">
+      <c r="AO11" s="18" t="str">
         <f t="array" ref="AO11">_xlfn.XLOOKUP($B11,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/izakaya_sei</v>
       </c>
@@ -3112,7 +3091,7 @@
         <f t="array" ref="AP11">_xlfn.XLOOKUP($B11,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目３−１１</v>
       </c>
-      <c r="AQ11" s="17" t="str">
+      <c r="AQ11" s="18" t="str">
         <f t="array" ref="AQ11">_xlfn.XLOOKUP($B11,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/2TSaY99KjvafbH728</v>
       </c>
@@ -3125,25 +3104,25 @@
         <v>21</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J12" s="15">
         <v>0.625</v>
@@ -3152,19 +3131,19 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA12" s="14" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="AB12" s="14" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="AD12" s="14">
         <v>1000.0</v>
@@ -3173,13 +3152,13 @@
         <v>330.0</v>
       </c>
       <c r="AG12" s="14" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="AH12" s="14" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="AI12" s="14" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="AL12" s="14">
         <v>10.0</v>
@@ -3192,7 +3171,7 @@
         <f t="array" ref="AN12">_xlfn.XLOOKUP($B12,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>創作ガチ中華</v>
       </c>
-      <c r="AO12" s="17" t="str">
+      <c r="AO12" s="18" t="str">
         <f t="array" ref="AO12">_xlfn.XLOOKUP($B12,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/taipan_taisho</v>
       </c>
@@ -3200,7 +3179,7 @@
         <f t="array" ref="AP12">_xlfn.XLOOKUP($B12,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目５−１３</v>
       </c>
-      <c r="AQ12" s="17" t="str">
+      <c r="AQ12" s="18" t="str">
         <f t="array" ref="AQ12">_xlfn.XLOOKUP($B12,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/wSUzPpSDHh3tzyap6</v>
       </c>
@@ -3213,25 +3192,25 @@
         <v>16</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J13" s="15">
         <v>0.625</v>
@@ -3240,43 +3219,43 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA13" s="14" t="s">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="AB13" s="14" t="s">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="AD13" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="AE13" s="14" t="s">
-        <v>371</v>
+        <v>407</v>
+      </c>
+      <c r="AD13" s="22">
+        <v>2000.0</v>
+      </c>
+      <c r="AE13" s="14">
+        <v>0.0</v>
       </c>
       <c r="AF13" s="14" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="AG13" s="14" t="s">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="AH13" s="14" t="s">
-        <v>375</v>
-      </c>
-      <c r="AI13" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="AL13" s="14" t="s">
-        <v>376</v>
+        <v>410</v>
+      </c>
+      <c r="AI13" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="AL13" s="14">
+        <v>10.0</v>
       </c>
       <c r="AM13" s="16">
         <f t="array" ref="AM13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3286,7 +3265,7 @@
         <f t="array" ref="AN13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>通える高級焼肉</v>
       </c>
-      <c r="AO13" s="17" t="str">
+      <c r="AO13" s="18" t="str">
         <f t="array" ref="AO13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/sunnasubi0675085821</v>
       </c>
@@ -3294,7 +3273,7 @@
         <f t="array" ref="AP13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目５−１０</v>
       </c>
-      <c r="AQ13" s="17" t="str">
+      <c r="AQ13" s="18" t="str">
         <f t="array" ref="AQ13">_xlfn.XLOOKUP($B13,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/9DHWbdXcG6VwQRg17</v>
       </c>
@@ -3304,28 +3283,28 @@
         <v>46300.61462475694</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J14" s="15">
         <v>0.8333333333357587</v>
@@ -3334,28 +3313,28 @@
         <v>0.14583333333575865</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>392</v>
+        <v>411</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O14" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="R14" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>254</v>
+        <v>415</v>
+      </c>
+      <c r="S14" s="14">
+        <v>1000.0</v>
       </c>
       <c r="AL14" s="14">
         <v>15.0</v>
@@ -3368,7 +3347,7 @@
         <f t="array" ref="AN14">_xlfn.XLOOKUP($B14,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>カジュアルバー</v>
       </c>
-      <c r="AO14" s="17" t="str">
+      <c r="AO14" s="18" t="str">
         <f t="array" ref="AO14">_xlfn.XLOOKUP($B14,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/bar_cococolor_taisho</v>
       </c>
@@ -3376,7 +3355,7 @@
         <f t="array" ref="AP14">_xlfn.XLOOKUP($B14,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目１６−１６</v>
       </c>
-      <c r="AQ14" s="17" t="str">
+      <c r="AQ14" s="18" t="str">
         <f t="array" ref="AQ14">_xlfn.XLOOKUP($B14,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/95uXqnFcfkMM8Jwo8</v>
       </c>
@@ -3386,28 +3365,28 @@
         <v>46304.76113125</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="J15" s="15">
         <v>0.8125</v>
@@ -3416,19 +3395,19 @@
         <v>0.9930555555547471</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA15" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="AB15" s="14" t="s">
         <v>418</v>
-      </c>
-      <c r="AB15" s="14" t="s">
-        <v>419</v>
       </c>
       <c r="AD15" s="14">
         <v>100.0</v>
@@ -3437,16 +3416,16 @@
         <v>0.0</v>
       </c>
       <c r="AF15" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="AG15" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="AH15" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="AG15" s="14" t="s">
-        <v>423</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>424</v>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>425</v>
+      <c r="AI15" s="14">
+        <v>100.0</v>
       </c>
       <c r="AJ15" s="14">
         <v>0.0</v>
@@ -3462,7 +3441,7 @@
         <f t="array" ref="AN15">_xlfn.XLOOKUP($B15,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>生演奏で歌えるバー</v>
       </c>
-      <c r="AO15" s="17" t="str">
+      <c r="AO15" s="18" t="str">
         <f t="array" ref="AO15">_xlfn.XLOOKUP($B15,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/9kaino_omote</v>
       </c>
@@ -3470,7 +3449,7 @@
         <f t="array" ref="AP15">_xlfn.XLOOKUP($B15,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区泉尾４丁目４−１</v>
       </c>
-      <c r="AQ15" s="17" t="str">
+      <c r="AQ15" s="18" t="str">
         <f t="array" ref="AQ15">_xlfn.XLOOKUP($B15,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/omY9WnpdAGAU7iFX6</v>
       </c>
@@ -3480,28 +3459,28 @@
         <v>46304.852581238425</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J16" s="15">
         <v>0.47916666666424135</v>
@@ -3510,43 +3489,43 @@
         <v>0.625</v>
       </c>
       <c r="L16" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="AA16" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="AB16" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="AD16" s="14">
+        <v>800.0</v>
+      </c>
+      <c r="AF16" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="AG16" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="M16" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="N16" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="O16" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="AA16" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="AB16" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="AD16" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="AF16" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="AG16" s="14" t="s">
-        <v>436</v>
-      </c>
       <c r="AH16" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>440</v>
+        <v>430</v>
+      </c>
+      <c r="AI16" s="22">
+        <v>1250.0</v>
       </c>
       <c r="AK16" s="14" t="s">
-        <v>441</v>
-      </c>
-      <c r="AL16" s="14" t="s">
-        <v>442</v>
+        <v>431</v>
+      </c>
+      <c r="AL16" s="14">
+        <v>5.0</v>
       </c>
       <c r="AM16" s="16">
         <f t="array" ref="AM16">_xlfn.XLOOKUP($B16,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3556,7 +3535,7 @@
         <f t="array" ref="AN16">_xlfn.XLOOKUP($B16,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>デートの行き先、カレー屋</v>
       </c>
-      <c r="AO16" s="17" t="str">
+      <c r="AO16" s="18" t="str">
         <f t="array" ref="AO16">_xlfn.XLOOKUP($B16,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/sheandcurry</v>
       </c>
@@ -3574,28 +3553,28 @@
         <v>46305.67339996528</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="J17" s="15">
         <v>0.7083333333357587</v>
@@ -3604,22 +3583,22 @@
         <v>0.8958333333357587</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O17" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="S17" s="14" t="s">
-        <v>448</v>
+        <v>436</v>
+      </c>
+      <c r="S17" s="14">
+        <v>700.0</v>
       </c>
       <c r="AL17" s="14">
         <v>10.0</v>
@@ -3632,7 +3611,7 @@
         <f t="array" ref="AN17">_xlfn.XLOOKUP($B17,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>立ち飲み・ホルモン</v>
       </c>
-      <c r="AO17" s="17" t="str">
+      <c r="AO17" s="18" t="str">
         <f t="array" ref="AO17">_xlfn.XLOOKUP($B17,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/bbq.mou.29</v>
       </c>
@@ -3640,7 +3619,7 @@
         <f t="array" ref="AP17">_xlfn.XLOOKUP($B17,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目２−４</v>
       </c>
-      <c r="AQ17" s="17" t="str">
+      <c r="AQ17" s="18" t="str">
         <f t="array" ref="AQ17">_xlfn.XLOOKUP($B17,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/kCXY14AkjvY7xeAX8</v>
       </c>
@@ -3650,28 +3629,28 @@
         <v>46305.71587197916</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="J18" s="15">
         <v>0.7708333333357587</v>
@@ -3680,31 +3659,31 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O18" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA18" s="14" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="AB18" s="14" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="AD18" s="14">
         <v>500.0</v>
       </c>
       <c r="AG18" s="14" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="AH18" s="14" t="s">
-        <v>453</v>
-      </c>
-      <c r="AI18" s="14" t="s">
-        <v>255</v>
+        <v>441</v>
+      </c>
+      <c r="AI18" s="14">
+        <v>500.0</v>
       </c>
       <c r="AL18" s="14">
         <v>10.0</v>
@@ -3717,7 +3696,7 @@
         <f t="array" ref="AN18">_xlfn.XLOOKUP($B18,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>素朴な家庭料理</v>
       </c>
-      <c r="AO18" s="17" t="str">
+      <c r="AO18" s="18" t="str">
         <f t="array" ref="AO18">_xlfn.XLOOKUP($B18,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/syuugo_ma_0418</v>
       </c>
@@ -3735,28 +3714,28 @@
         <v>46305.73525341435</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="J19" s="15">
         <v>0.7083333333357587</v>
@@ -3765,28 +3744,28 @@
         <v>0.875</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O19" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA19" s="14" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AB19" s="14" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AD19" s="14">
         <v>1000.0</v>
       </c>
       <c r="AG19" s="14" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="AH19" s="14" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="AI19" s="14">
         <v>100.0</v>
@@ -3802,7 +3781,7 @@
         <f t="array" ref="AN19">_xlfn.XLOOKUP($B19,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v/>
       </c>
-      <c r="AO19" s="17" t="str">
+      <c r="AO19" s="18" t="str">
         <f t="array" ref="AO19">_xlfn.XLOOKUP($B19,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/ippainomi.hana0806</v>
       </c>
@@ -3810,7 +3789,7 @@
         <f t="array" ref="AP19">_xlfn.XLOOKUP($B19,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区千島3丁目4-7</v>
       </c>
-      <c r="AQ19" s="17" t="str">
+      <c r="AQ19" s="18" t="str">
         <f t="array" ref="AQ19">_xlfn.XLOOKUP($B19,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/qxCPY32XRzxQ52ni7</v>
       </c>
@@ -3820,28 +3799,28 @@
         <v>46305.85531787037</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="J20" s="15">
         <v>0.8333333333357587</v>
@@ -3850,25 +3829,25 @@
         <v>0.9583333333357587</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="V20" s="14" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="W20" s="14" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="X20" s="14" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Y20" s="14" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="AL20" s="14">
         <v>2.0</v>
@@ -3881,7 +3860,7 @@
         <f t="array" ref="AN20">_xlfn.XLOOKUP($B20,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>楽しく呑めて歌える憩いの場</v>
       </c>
-      <c r="AO20" s="17" t="str">
+      <c r="AO20" s="18" t="str">
         <f t="array" ref="AO20">_xlfn.XLOOKUP($B20,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/__2knme0703</v>
       </c>
@@ -3899,10 +3878,10 @@
         <v>46306.81166831018</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="AM21" s="16">
         <f t="array" ref="AM21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
@@ -3912,7 +3891,7 @@
         <f t="array" ref="AN21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>創作料理居酒屋</v>
       </c>
-      <c r="AO21" s="17" t="str">
+      <c r="AO21" s="18" t="str">
         <f t="array" ref="AO21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/fujiwarakun_taisho</v>
       </c>
@@ -3920,7 +3899,7 @@
         <f t="array" ref="AP21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目１−７</v>
       </c>
-      <c r="AQ21" s="17" t="str">
+      <c r="AQ21" s="18" t="str">
         <f t="array" ref="AQ21">_xlfn.XLOOKUP($B21,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/svhsvpjHHy4Wfxv49</v>
       </c>
@@ -3930,28 +3909,28 @@
         <v>46309.79352489584</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>465</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>145</v>
-      </c>
       <c r="H22" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="J22" s="15">
         <v>0.7083333333357587</v>
@@ -3960,52 +3939,52 @@
         <v>0.9166666666642413</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="R22" s="14" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="S22" s="14">
         <v>1000.0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="U22" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="AL22" s="14">
         <v>5.0</v>
       </c>
-      <c r="AM22" s="24">
+      <c r="AM22" s="25">
         <f t="array" ref="AM22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
         <v>21</v>
       </c>
-      <c r="AN22" s="24" t="str">
+      <c r="AN22" s="25" t="str">
         <f t="array" ref="AN22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>お好み・焼きそば・鉄板居酒屋</v>
       </c>
-      <c r="AO22" s="25" t="str">
+      <c r="AO22" s="26" t="str">
         <f t="array" ref="AO22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/teppanyaki_eihachi</v>
       </c>
-      <c r="AP22" s="24" t="str">
+      <c r="AP22" s="25" t="str">
         <f t="array" ref="AP22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家西１丁目６−３</v>
       </c>
-      <c r="AQ22" s="25" t="str">
+      <c r="AQ22" s="26" t="str">
         <f t="array" ref="AQ22">_xlfn.XLOOKUP($B22,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/SgdnoFYhwHF52vjd8</v>
       </c>
@@ -4015,28 +3994,28 @@
         <v>46310.973587430555</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="J23" s="15">
         <v>0.47916666666424135</v>
@@ -4045,25 +4024,25 @@
         <v>0.0</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="S23" s="14" t="s">
-        <v>254</v>
+        <v>463</v>
+      </c>
+      <c r="S23" s="14">
+        <v>1000.0</v>
       </c>
       <c r="U23" s="14">
         <v>30.0</v>
@@ -4071,23 +4050,23 @@
       <c r="AL23" s="14">
         <v>10.0</v>
       </c>
-      <c r="AM23" s="24">
+      <c r="AM23" s="25">
         <f t="array" ref="AM23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
         <v>32</v>
       </c>
-      <c r="AN23" s="24" t="str">
+      <c r="AN23" s="25" t="str">
         <f t="array" ref="AN23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>イタリアン・メキシカン・アメリカン</v>
       </c>
-      <c r="AO23" s="25" t="str">
+      <c r="AO23" s="26" t="str">
         <f t="array" ref="AO23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/tms_diner_osaka</v>
       </c>
-      <c r="AP23" s="24" t="str">
+      <c r="AP23" s="25" t="str">
         <f t="array" ref="AP23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目２−５ 2F</v>
       </c>
-      <c r="AQ23" s="25" t="str">
+      <c r="AQ23" s="26" t="str">
         <f t="array" ref="AQ23">_xlfn.XLOOKUP($B23,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/qM8P7SU6UqcARZm29</v>
       </c>
@@ -4097,28 +4076,28 @@
         <v>46312.58616018519</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="J24" s="15">
         <v>0.7916666666642413</v>
@@ -4127,49 +4106,49 @@
         <v>0.0</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O24" s="14" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="V24" s="14" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="W24" s="14" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="X24" s="14">
         <v>100.0</v>
       </c>
       <c r="Y24" s="14" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="AL24" s="14">
         <v>10.0</v>
       </c>
-      <c r="AM24" s="24">
+      <c r="AM24" s="25">
         <f t="array" ref="AM24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
         <v>53</v>
       </c>
-      <c r="AN24" s="24" t="str">
+      <c r="AN24" s="25" t="str">
         <f t="array" ref="AN24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>アットホームなカラオケBAR</v>
       </c>
-      <c r="AO24" s="25" t="str">
+      <c r="AO24" s="26" t="str">
         <f t="array" ref="AO24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/3piece_osake</v>
       </c>
-      <c r="AP24" s="24" t="str">
+      <c r="AP24" s="25" t="str">
         <f t="array" ref="AP24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区南恩加島６丁目７−８</v>
       </c>
-      <c r="AQ24" s="25" t="str">
+      <c r="AQ24" s="26" t="str">
         <f t="array" ref="AQ24">_xlfn.XLOOKUP($B24,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/67gvLqPdoESWNqod7</v>
       </c>
@@ -4179,28 +4158,28 @@
         <v>46315.68812100694</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="J25" s="15">
         <v>0.7291666666642413</v>
@@ -4209,52 +4188,52 @@
         <v>0.9583333333357587</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="R25" s="14" t="s">
-        <v>485</v>
-      </c>
-      <c r="S25" s="14" t="s">
-        <v>486</v>
+        <v>473</v>
+      </c>
+      <c r="S25" s="14">
+        <v>1100.0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="U25" s="14" t="s">
-        <v>313</v>
+        <v>390</v>
       </c>
       <c r="AL25" s="14">
         <v>10.0</v>
       </c>
-      <c r="AM25" s="24">
+      <c r="AM25" s="25">
         <f t="array" ref="AM25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
         <v>9</v>
       </c>
-      <c r="AN25" s="24" t="str">
+      <c r="AN25" s="25" t="str">
         <f t="array" ref="AN25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>焼き鳥・お出汁料理</v>
       </c>
-      <c r="AO25" s="25" t="str">
+      <c r="AO25" s="26" t="str">
         <f t="array" ref="AO25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/chabo_taisho</v>
       </c>
-      <c r="AP25" s="24" t="str">
+      <c r="AP25" s="25" t="str">
         <f t="array" ref="AP25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区三軒家東１丁目１７−１６</v>
       </c>
-      <c r="AQ25" s="25" t="str">
+      <c r="AQ25" s="26" t="str">
         <f t="array" ref="AQ25">_xlfn.XLOOKUP($B25,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/a9AcRcjV9q895Jeo6</v>
       </c>
@@ -4264,28 +4243,28 @@
         <v>46315.72136438657</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="J26" s="15">
         <v>0.7083333333357587</v>
@@ -4294,69 +4273,148 @@
         <v>0.41666666666424135</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>334</v>
+        <v>395</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="O26" s="14" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="AA26" s="14" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="AB26" s="14" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="AC26" s="14" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AD26" s="14" t="s">
-        <v>254</v>
+        <v>478</v>
       </c>
       <c r="AE26" s="14">
         <v>0.0</v>
       </c>
       <c r="AF26" s="14" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="AG26" s="14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AH26" s="14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AI26" s="14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AJ26" s="14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AK26" s="14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AL26" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="AM26" s="24">
+        <v>481</v>
+      </c>
+      <c r="AM26" s="25">
         <f t="array" ref="AM26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
         <v>44</v>
       </c>
-      <c r="AN26" s="24" t="str">
+      <c r="AN26" s="25" t="str">
         <f t="array" ref="AN26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
         <v>変態植物倶楽部の店</v>
       </c>
-      <c r="AO26" s="25" t="str">
+      <c r="AO26" s="26" t="str">
         <f t="array" ref="AO26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
         <v>https://www.instagram.com/pureko.yakisoba___</v>
       </c>
-      <c r="AP26" s="24" t="str">
+      <c r="AP26" s="25" t="str">
         <f t="array" ref="AP26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
         <v>大阪市大正区泉尾１丁目２２−１２</v>
       </c>
-      <c r="AQ26" s="25" t="str">
+      <c r="AQ26" s="26" t="str">
         <f t="array" ref="AQ26">_xlfn.XLOOKUP($B26,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
         <v>https://maps.app.goo.gl/7LxwLtzxhZXxzxw59</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="13">
+        <v>46315.925904918986</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="J27" s="15">
+        <v>0.7916666666642413</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0.08333333333575865</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q27" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="R27" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="S27" s="14">
+        <v>1000.0</v>
+      </c>
+      <c r="AL27" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="AM27" s="25">
+        <f t="array" ref="AM27">_xlfn.XLOOKUP($B27,'シート1'!$B$2:$B$61,'シート1'!$A$2:$A$61,"",0,1)</f>
+        <v>40</v>
+      </c>
+      <c r="AN27" s="25" t="str">
+        <f t="array" ref="AN27">_xlfn.XLOOKUP($B27,'シート1'!$B$2:$B$61,'シート1'!C$2:C$61,"",0,1)</f>
+        <v>お酒&amp;カルチャー発信場所</v>
+      </c>
+      <c r="AO27" s="26" t="str">
+        <f t="array" ref="AO27">_xlfn.XLOOKUP($B27,'シート1'!$B$2:$B$61,'シート1'!D$2:D$61,"",0,1)</f>
+        <v>https://www.instagram.com/bar_edit_osaka</v>
+      </c>
+      <c r="AP27" s="25" t="str">
+        <f t="array" ref="AP27">_xlfn.XLOOKUP($B27,'シート1'!$B$2:$B$61,'シート1'!E$2:E$61,"",0,1)</f>
+        <v>大阪市大正区泉尾１丁目３０−１５ 平本ビル</v>
+      </c>
+      <c r="AQ27" s="26" t="str">
+        <f t="array" ref="AQ27">_xlfn.XLOOKUP($B27,'シート1'!$B$2:$B$61,'シート1'!F$2:F$61,"",0,1)</f>
+        <v>https://maps.app.goo.gl/o8GMyay7XvnYpEwk7</v>
       </c>
     </row>
   </sheetData>
@@ -4496,10 +4554,10 @@
         <v>28</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -4507,19 +4565,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -4527,19 +4585,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -4547,19 +4605,19 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -4567,19 +4625,19 @@
         <v>34.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>88</v>
+        <v>62</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -4587,19 +4645,19 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -4607,19 +4665,19 @@
         <v>10.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -4627,19 +4685,19 @@
         <v>11.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -4647,19 +4705,19 @@
         <v>12.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -4667,19 +4725,19 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -4687,19 +4745,19 @@
         <v>14.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -4707,19 +4765,19 @@
         <v>15.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
@@ -4727,19 +4785,19 @@
         <v>16.0</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -4747,19 +4805,19 @@
         <v>17.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -4767,19 +4825,19 @@
         <v>18.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
@@ -4787,19 +4845,19 @@
         <v>19.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -4807,19 +4865,19 @@
         <v>29.0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23">
@@ -4827,19 +4885,19 @@
         <v>21.0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>180</v>
+        <v>164</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
@@ -4847,19 +4905,19 @@
         <v>22.0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>187</v>
+        <v>169</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>170</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25">
@@ -4867,19 +4925,19 @@
         <v>23.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26">
@@ -4887,16 +4945,16 @@
         <v>24.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="F26" s="19"/>
     </row>
@@ -4905,16 +4963,16 @@
         <v>25.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="18" t="s">
-        <v>210</v>
+        <v>191</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>192</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="F27" s="19"/>
     </row>
@@ -4923,19 +4981,19 @@
         <v>26.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>216</v>
+        <v>195</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>196</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29">
@@ -4943,19 +5001,19 @@
         <v>27.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>227</v>
+        <v>200</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>201</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30">
@@ -4963,19 +5021,19 @@
         <v>28.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>232</v>
+        <v>209</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>210</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
@@ -4983,19 +5041,19 @@
         <v>35.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>237</v>
+        <v>215</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>216</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>242</v>
+        <v>218</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="32">
@@ -5003,19 +5061,19 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>246</v>
+        <v>220</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33">
@@ -5023,19 +5081,19 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34">
@@ -5043,19 +5101,19 @@
         <v>31.0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>270</v>
+        <v>235</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35">
@@ -5063,19 +5121,19 @@
         <v>32.0</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
     </row>
     <row r="36">
@@ -5083,19 +5141,19 @@
         <v>33.0</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>279</v>
+        <v>244</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37">
@@ -5103,16 +5161,16 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>283</v>
+        <v>247</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>248</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>284</v>
+        <v>249</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="F37" s="19"/>
     </row>
@@ -5121,16 +5179,16 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="F38" s="19"/>
     </row>
@@ -5139,16 +5197,16 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="F39" s="19"/>
     </row>
@@ -5157,16 +5215,16 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="F40" s="19"/>
     </row>
@@ -5175,19 +5233,19 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>305</v>
+        <v>275</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="42">
@@ -5195,19 +5253,19 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>314</v>
+        <v>173</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="43">
@@ -5215,19 +5273,19 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>321</v>
+        <v>284</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="44">
@@ -5235,19 +5293,19 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>326</v>
+        <v>289</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="45">
@@ -5255,19 +5313,19 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>333</v>
+        <v>296</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="46">
@@ -5275,16 +5333,16 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="F46" s="19"/>
     </row>
@@ -5293,55 +5351,55 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="F47" s="22"/>
+        <v>309</v>
+      </c>
+      <c r="F47" s="23"/>
     </row>
     <row r="48">
       <c r="A48" s="3">
         <v>47.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>346</v>
+        <v>312</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="F48" s="22"/>
+        <v>313</v>
+      </c>
+      <c r="F48" s="23"/>
     </row>
     <row r="49">
       <c r="A49" s="3">
         <v>48.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>354</v>
+        <v>317</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="50">
@@ -5349,19 +5407,19 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>360</v>
+        <v>321</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>362</v>
+        <v>322</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="51">
@@ -5369,19 +5427,19 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>370</v>
+        <v>326</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>378</v>
+        <v>329</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="52">
@@ -5389,19 +5447,19 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>379</v>
+        <v>333</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>380</v>
+        <v>334</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>381</v>
+        <v>335</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>383</v>
+        <v>337</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="53">
@@ -5409,19 +5467,19 @@
         <v>52.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>384</v>
+        <v>342</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>386</v>
+        <v>344</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>388</v>
+        <v>347</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="54">
@@ -5429,19 +5487,19 @@
         <v>53.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>391</v>
+        <v>355</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>396</v>
+        <v>357</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="55">
@@ -5449,19 +5507,19 @@
         <v>54.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>401</v>
+        <v>361</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>403</v>
+        <v>362</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="56">
@@ -5469,17 +5527,17 @@
         <v>55.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="C56" s="23"/>
+        <v>364</v>
+      </c>
+      <c r="C56" s="24"/>
       <c r="D56" s="5" t="s">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>407</v>
+        <v>366</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="57">
@@ -5487,17 +5545,17 @@
         <v>56.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C57" s="23"/>
+        <v>368</v>
+      </c>
+      <c r="C57" s="24"/>
       <c r="D57" s="5" t="s">
-        <v>409</v>
+        <v>369</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>410</v>
+        <v>366</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="58">
@@ -5505,17 +5563,17 @@
         <v>57.0</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="C58" s="23"/>
+        <v>371</v>
+      </c>
+      <c r="C58" s="24"/>
       <c r="D58" s="5" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>415</v>
+        <v>376</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="59">
@@ -5523,17 +5581,17 @@
         <v>58.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C59" s="23"/>
+        <v>378</v>
+      </c>
+      <c r="C59" s="24"/>
       <c r="D59" s="5" t="s">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>422</v>
+        <v>380</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="60">
@@ -5541,11 +5599,11 @@
         <v>59.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C60" s="23"/>
+        <v>382</v>
+      </c>
+      <c r="C60" s="24"/>
       <c r="D60" s="5" t="s">
-        <v>431</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61">
@@ -5553,11 +5611,11 @@
         <v>60.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="C61" s="23"/>
+        <v>384</v>
+      </c>
+      <c r="C61" s="24"/>
       <c r="D61" s="5" t="s">
-        <v>438</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
